--- a/research/traditional_assets/database/data/uganda/uganda_drugs_pharmaceutical.xlsx
+++ b/research/traditional_assets/database/data/uganda/uganda_drugs_pharmaceutical.xlsx
@@ -638,10 +638,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="AB2">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -745,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="AB3">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -1039,37 +1039,37 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="G2">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="H2">
-        <v>78.7828663279145</v>
+        <v>51.197701046633</v>
       </c>
       <c r="I2">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="J2">
-        <v>100.563866327915</v>
+        <v>63.860701046633</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>21.781</v>
+        <v>12.663</v>
       </c>
       <c r="M2">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="N2">
-        <v>0.105761370150201</v>
+        <v>0.183903881727839</v>
       </c>
       <c r="O2">
-        <v>0.0491193792233793</v>
+        <v>0.0882712844036697</v>
       </c>
       <c r="P2">
-        <v>0.0195747550639126</v>
+        <v>0.0441</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -1078,23 +1078,23 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="S2">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="T2">
-        <v>0.131505424007145</v>
+        <v>0.221066938895998</v>
       </c>
       <c r="U2">
-        <v>1.01962643624273</v>
+        <v>0.997353358654514</v>
       </c>
       <c r="V2">
-        <v>1.23282105472984</v>
+        <v>1.18293683172061</v>
       </c>
       <c r="W2">
-        <v>4.598720313564579</v>
+        <v>3.511041416750965</v>
       </c>
       <c r="X2">
         <v>0</v>
@@ -1103,16 +1103,16 @@
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>0.0151</v>
+        <v>0.0388</v>
       </c>
       <c r="AA2">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="AB2">
-        <v>0.09442199543927605</v>
+        <v>0.1540800269367614</v>
       </c>
       <c r="AC2">
-        <v>0.07017054174768475</v>
+        <v>0.1261018348623854</v>
       </c>
       <c r="AD2">
         <v>0.3</v>
@@ -1301,13 +1301,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="C2">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="D2">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1319,7 +1319,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1340,7 +1340,7 @@
         <v>2.801</v>
       </c>
       <c r="O2">
-        <v>0.8403</v>
+        <v>0.8403000000000002</v>
       </c>
       <c r="P2">
         <v>1.9607</v>
@@ -1352,19 +1352,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.111375162712676</v>
+        <v>0.192472232366957</v>
       </c>
       <c r="T2">
-        <v>1.019626436242726</v>
+        <v>0.9973533586545144</v>
       </c>
       <c r="U2">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V2">
         <v>0.3</v>
       </c>
       <c r="W2">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1383,25 +1383,25 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1110876594770878</v>
+        <v>0.1919431156698562</v>
       </c>
       <c r="C3">
-        <v>94.03664642453546</v>
+        <v>59.90533934777691</v>
       </c>
       <c r="D3">
-        <v>94.98364642453546</v>
+        <v>60.50833934777691</v>
       </c>
       <c r="E3">
-        <v>0.9470000000000001</v>
+        <v>0.603</v>
       </c>
       <c r="F3">
-        <v>0.9470000000000001</v>
+        <v>0.603</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1416,37 +1416,37 @@
         <v>2.801</v>
       </c>
       <c r="M3">
-        <v>0.02060702473781454</v>
+        <v>0.0275571</v>
       </c>
       <c r="N3">
-        <v>2.780392975262186</v>
+        <v>2.7734429</v>
       </c>
       <c r="O3">
-        <v>0.8341178925786557</v>
+        <v>0.8320328700000001</v>
       </c>
       <c r="P3">
-        <v>1.94627508268353</v>
+        <v>1.94141003</v>
       </c>
       <c r="Q3">
-        <v>2.34527508268353</v>
+        <v>2.34041003</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.112055896186402</v>
+        <v>0.1935588037069254</v>
       </c>
       <c r="T3">
-        <v>1.026835916094947</v>
+        <v>1.004405352099546</v>
       </c>
       <c r="U3">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
         <v>0.3</v>
       </c>
       <c r="W3">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>135.9245226148575</v>
+        <v>101.6434965943441</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1465,25 +1465,25 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.1108001562414996</v>
+        <v>0.1914139989727553</v>
       </c>
       <c r="C4">
-        <v>93.37499711514566</v>
+        <v>59.51212333141048</v>
       </c>
       <c r="D4">
-        <v>95.26899711514567</v>
+        <v>60.71812333141048</v>
       </c>
       <c r="E4">
-        <v>1.894</v>
+        <v>1.206</v>
       </c>
       <c r="F4">
-        <v>1.894</v>
+        <v>1.206</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -1498,37 +1498,37 @@
         <v>2.801</v>
       </c>
       <c r="M4">
-        <v>0.04121404947562907</v>
+        <v>0.0551142</v>
       </c>
       <c r="N4">
-        <v>2.759785950524371</v>
+        <v>2.7458858</v>
       </c>
       <c r="O4">
-        <v>0.8279357851573114</v>
+        <v>0.8237657400000001</v>
       </c>
       <c r="P4">
-        <v>1.93185016536706</v>
+        <v>1.92212006</v>
       </c>
       <c r="Q4">
-        <v>2.33085016536706</v>
+        <v>2.32112006</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1127505221799999</v>
+        <v>0.1946675499721993</v>
       </c>
       <c r="T4">
-        <v>1.034192528189051</v>
+        <v>1.01160126377815</v>
       </c>
       <c r="U4">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V4">
         <v>0.3</v>
       </c>
       <c r="W4">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>67.96226130742876</v>
+        <v>50.82174829717205</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1547,25 +1547,25 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1105126530059114</v>
+        <v>0.1908848822756544</v>
       </c>
       <c r="C5">
-        <v>92.71506747802668</v>
+        <v>59.12036702894677</v>
       </c>
       <c r="D5">
-        <v>95.55606747802668</v>
+        <v>60.92936702894676</v>
       </c>
       <c r="E5">
-        <v>2.841</v>
+        <v>1.809</v>
       </c>
       <c r="F5">
-        <v>2.841</v>
+        <v>1.809</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1580,37 +1580,37 @@
         <v>2.801</v>
       </c>
       <c r="M5">
-        <v>0.06182107421344361</v>
+        <v>0.0826713</v>
       </c>
       <c r="N5">
-        <v>2.739178925786557</v>
+        <v>2.7183287</v>
       </c>
       <c r="O5">
-        <v>0.821753677735967</v>
+        <v>0.8154986100000002</v>
       </c>
       <c r="P5">
-        <v>1.91742524805059</v>
+        <v>1.90283009</v>
       </c>
       <c r="Q5">
-        <v>2.31642524805059</v>
+        <v>2.30183009</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.1134594703590329</v>
+        <v>0.1957991569852107</v>
       </c>
       <c r="T5">
-        <v>1.041700823006744</v>
+        <v>1.018945544769715</v>
       </c>
       <c r="U5">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V5">
         <v>0.3</v>
       </c>
       <c r="W5">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>45.3081742049525</v>
+        <v>33.88116553144804</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1629,25 +1629,25 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1102251497703232</v>
+        <v>0.1903557655785535</v>
       </c>
       <c r="C6">
-        <v>92.05687310562725</v>
+        <v>58.7300857289958</v>
       </c>
       <c r="D6">
-        <v>95.84487310562724</v>
+        <v>61.1420857289958</v>
       </c>
       <c r="E6">
-        <v>3.788</v>
+        <v>2.412</v>
       </c>
       <c r="F6">
-        <v>3.788</v>
+        <v>2.412</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -1662,37 +1662,37 @@
         <v>2.801</v>
       </c>
       <c r="M6">
-        <v>0.08242809895125815</v>
+        <v>0.1102284</v>
       </c>
       <c r="N6">
-        <v>2.718571901048742</v>
+        <v>2.6907716</v>
       </c>
       <c r="O6">
-        <v>0.8155715703146226</v>
+        <v>0.8072314800000001</v>
       </c>
       <c r="P6">
-        <v>1.90300033073412</v>
+        <v>1.88354012</v>
       </c>
       <c r="Q6">
-        <v>2.30200033073412</v>
+        <v>2.28254012</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1141831882917957</v>
+        <v>0.1969543391443266</v>
       </c>
       <c r="T6">
-        <v>1.049365540633139</v>
+        <v>1.026442831615271</v>
       </c>
       <c r="U6">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V6">
         <v>0.3</v>
       </c>
       <c r="W6">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.98113065371438</v>
+        <v>25.41087414858603</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1711,25 +1711,25 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.109937646534735</v>
+        <v>0.1898266488814527</v>
       </c>
       <c r="C7">
-        <v>91.40042977947209</v>
+        <v>58.34129493442004</v>
       </c>
       <c r="D7">
-        <v>96.13542977947209</v>
+        <v>61.35629493442004</v>
       </c>
       <c r="E7">
-        <v>4.735</v>
+        <v>3.015</v>
       </c>
       <c r="F7">
-        <v>4.735</v>
+        <v>3.015</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -1744,37 +1744,37 @@
         <v>2.801</v>
       </c>
       <c r="M7">
-        <v>0.1030351236890727</v>
+        <v>0.1377855</v>
       </c>
       <c r="N7">
-        <v>2.697964876310928</v>
+        <v>2.6632145</v>
       </c>
       <c r="O7">
-        <v>0.8093894628932783</v>
+        <v>0.7989643500000001</v>
       </c>
       <c r="P7">
-        <v>1.888575413417649</v>
+        <v>1.86425015</v>
       </c>
       <c r="Q7">
-        <v>2.287575413417649</v>
+        <v>2.26325015</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.114922142391564</v>
+        <v>0.1981338409278449</v>
       </c>
       <c r="T7">
-        <v>1.057191620735879</v>
+        <v>1.034097956078628</v>
       </c>
       <c r="U7">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V7">
         <v>0.3</v>
       </c>
       <c r="W7">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.1849045229715</v>
+        <v>20.32869931886882</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1793,25 +1793,25 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1096501432991469</v>
+        <v>0.1892975321843518</v>
       </c>
       <c r="C8">
-        <v>90.7457534730366</v>
+        <v>57.95401036610087</v>
       </c>
       <c r="D8">
-        <v>96.4277534730366</v>
+        <v>61.57201036610088</v>
       </c>
       <c r="E8">
-        <v>5.682</v>
+        <v>3.618</v>
       </c>
       <c r="F8">
-        <v>5.682</v>
+        <v>3.618</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1826,37 +1826,37 @@
         <v>2.801</v>
       </c>
       <c r="M8">
-        <v>0.1236421484268872</v>
+        <v>0.1653426</v>
       </c>
       <c r="N8">
-        <v>2.677357851573113</v>
+        <v>2.6356574</v>
       </c>
       <c r="O8">
-        <v>0.8032073554719339</v>
+        <v>0.7906972200000002</v>
       </c>
       <c r="P8">
-        <v>1.874150496101179</v>
+        <v>1.84496018</v>
       </c>
       <c r="Q8">
-        <v>2.273150496101179</v>
+        <v>2.24396018</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.115676818918987</v>
+        <v>0.1993384384939913</v>
       </c>
       <c r="T8">
-        <v>1.065184213181231</v>
+        <v>1.041915955530567</v>
       </c>
       <c r="U8">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V8">
         <v>0.3</v>
       </c>
       <c r="W8">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.65408710247625</v>
+        <v>16.94058276572402</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1875,25 +1875,25 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1093626400635587</v>
+        <v>0.1887684154872509</v>
       </c>
       <c r="C9">
-        <v>90.09286035467395</v>
+        <v>57.56824796678448</v>
       </c>
       <c r="D9">
-        <v>96.72186035467395</v>
+        <v>61.78924796678448</v>
       </c>
       <c r="E9">
-        <v>6.629</v>
+        <v>4.221</v>
       </c>
       <c r="F9">
-        <v>6.629</v>
+        <v>4.221</v>
       </c>
       <c r="G9">
         <v>0</v>
       </c>
       <c r="H9">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -1908,37 +1908,37 @@
         <v>2.801</v>
       </c>
       <c r="M9">
-        <v>0.1442491731647018</v>
+        <v>0.1928997</v>
       </c>
       <c r="N9">
-        <v>2.656750826835299</v>
+        <v>2.6081003</v>
       </c>
       <c r="O9">
-        <v>0.7970252480505896</v>
+        <v>0.7824300900000002</v>
       </c>
       <c r="P9">
-        <v>1.859725578784709</v>
+        <v>1.82567021</v>
       </c>
       <c r="Q9">
-        <v>2.258725578784709</v>
+        <v>2.22467021</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1164477250491503</v>
+        <v>0.2005689413841408</v>
       </c>
       <c r="T9">
-        <v>1.073348689335085</v>
+        <v>1.049902084002978</v>
       </c>
       <c r="U9">
-        <v>0.02176032179283478</v>
+        <v>0.0457</v>
       </c>
       <c r="V9">
         <v>0.3</v>
       </c>
       <c r="W9">
-        <v>0.01523222525498434</v>
+        <v>0.03199</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.41778894497964</v>
+        <v>14.52049951347773</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -1957,25 +1957,25 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1090751368279705</v>
+        <v>0.1883288987901501</v>
       </c>
       <c r="C10">
-        <v>89.44176679059623</v>
+        <v>57.14686774999988</v>
       </c>
       <c r="D10">
-        <v>97.01776679059624</v>
+        <v>61.97086774999988</v>
       </c>
       <c r="E10">
-        <v>7.576000000000001</v>
+        <v>4.824</v>
       </c>
       <c r="F10">
-        <v>7.576000000000001</v>
+        <v>4.824</v>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1990,45 +1990,45 @@
         <v>2.801</v>
       </c>
       <c r="M10">
-        <v>0.1648561979025163</v>
+        <v>0.2281752</v>
       </c>
       <c r="N10">
-        <v>2.636143802097484</v>
+        <v>2.5728248</v>
       </c>
       <c r="O10">
-        <v>0.7908431406292451</v>
+        <v>0.7718474400000002</v>
       </c>
       <c r="P10">
-        <v>1.845300661468239</v>
+        <v>1.80097736</v>
       </c>
       <c r="Q10">
-        <v>2.244300661468238</v>
+        <v>2.19997736</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1172353900082302</v>
+        <v>0.2018261943371197</v>
       </c>
       <c r="T10">
-        <v>1.081690654100979</v>
+        <v>1.05806182396392</v>
       </c>
       <c r="U10">
-        <v>0.02176032179283478</v>
+        <v>0.0473</v>
       </c>
       <c r="V10">
         <v>0.3</v>
       </c>
       <c r="W10">
-        <v>0.01523222525498434</v>
+        <v>0.03311</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>16.99056532685719</v>
+        <v>12.27565484767845</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2039,25 +2039,25 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1087876335923823</v>
+        <v>0.1878109820930492</v>
       </c>
       <c r="C11">
-        <v>88.79248934791042</v>
+        <v>56.75925957341269</v>
       </c>
       <c r="D11">
-        <v>97.31548934791041</v>
+        <v>62.18625957341269</v>
       </c>
       <c r="E11">
-        <v>8.523</v>
+        <v>5.427</v>
       </c>
       <c r="F11">
-        <v>8.523</v>
+        <v>5.427</v>
       </c>
       <c r="G11">
         <v>0</v>
       </c>
       <c r="H11">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -2072,45 +2072,45 @@
         <v>2.801</v>
       </c>
       <c r="M11">
-        <v>0.1854632226403308</v>
+        <v>0.2566971</v>
       </c>
       <c r="N11">
-        <v>2.615536777359669</v>
+        <v>2.5443029</v>
       </c>
       <c r="O11">
-        <v>0.7846610332079007</v>
+        <v>0.7632908700000001</v>
       </c>
       <c r="P11">
-        <v>1.830875744151768</v>
+        <v>1.78101203</v>
       </c>
       <c r="Q11">
-        <v>2.229875744151768</v>
+        <v>2.18001203</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.118040366285092</v>
+        <v>0.203111079223131</v>
       </c>
       <c r="T11">
-        <v>1.090215958751838</v>
+        <v>1.066400898869058</v>
       </c>
       <c r="U11">
-        <v>0.02176032179283478</v>
+        <v>0.0473</v>
       </c>
       <c r="V11">
         <v>0.3</v>
       </c>
       <c r="W11">
-        <v>0.01523222525498434</v>
+        <v>0.03311</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>15.10272473498417</v>
+        <v>10.9116931979364</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2121,25 +2121,25 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1085001303567941</v>
+        <v>0.1875590653959484</v>
       </c>
       <c r="C12">
-        <v>88.14504479771003</v>
+        <v>56.26156916967221</v>
       </c>
       <c r="D12">
-        <v>97.61504479771003</v>
+        <v>62.29156916967221</v>
       </c>
       <c r="E12">
-        <v>9.470000000000001</v>
+        <v>6.03</v>
       </c>
       <c r="F12">
-        <v>9.470000000000001</v>
+        <v>6.03</v>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2154,45 +2154,45 @@
         <v>2.801</v>
       </c>
       <c r="M12">
-        <v>0.2060702473781454</v>
+        <v>0.308133</v>
       </c>
       <c r="N12">
-        <v>2.594929752621855</v>
+        <v>2.492867</v>
       </c>
       <c r="O12">
-        <v>0.7784789257865564</v>
+        <v>0.7478601000000002</v>
       </c>
       <c r="P12">
-        <v>1.816450826835298</v>
+        <v>1.7450069</v>
       </c>
       <c r="Q12">
-        <v>2.215450826835298</v>
+        <v>2.1440069</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1188632309236619</v>
+        <v>0.2044245171066093</v>
       </c>
       <c r="T12">
-        <v>1.09893071461716</v>
+        <v>1.074925286549866</v>
       </c>
       <c r="U12">
-        <v>0.02176032179283478</v>
+        <v>0.0511</v>
       </c>
       <c r="V12">
         <v>0.3</v>
       </c>
       <c r="W12">
-        <v>0.01523222525498434</v>
+        <v>0.03577</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.59245226148575</v>
+        <v>9.090230517341539</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2203,25 +2203,25 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1083347330207413</v>
+        <v>0.1870677486988475</v>
       </c>
       <c r="C13">
-        <v>87.37121275609988</v>
+        <v>55.86498552312908</v>
       </c>
       <c r="D13">
-        <v>97.78821275609988</v>
+        <v>62.49798552312908</v>
       </c>
       <c r="E13">
-        <v>10.417</v>
+        <v>6.633</v>
       </c>
       <c r="F13">
-        <v>10.417</v>
+        <v>6.633</v>
       </c>
       <c r="G13">
         <v>0</v>
       </c>
       <c r="H13">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2236,45 +2236,45 @@
         <v>2.801</v>
       </c>
       <c r="M13">
-        <v>0.2431964559530932</v>
+        <v>0.3389463</v>
       </c>
       <c r="N13">
-        <v>2.557803544046907</v>
+        <v>2.4620537</v>
       </c>
       <c r="O13">
-        <v>0.767341063214072</v>
+        <v>0.7386161100000002</v>
       </c>
       <c r="P13">
-        <v>1.790462480832835</v>
+        <v>1.72343759</v>
       </c>
       <c r="Q13">
-        <v>2.189462480832835</v>
+        <v>2.12243759</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1197045869024243</v>
+        <v>0.2057674704481432</v>
       </c>
       <c r="T13">
-        <v>1.107841307692939</v>
+        <v>1.083641233504399</v>
       </c>
       <c r="U13">
-        <v>0.02334611269589068</v>
+        <v>0.0511</v>
       </c>
       <c r="V13">
         <v>0.3</v>
       </c>
       <c r="W13">
-        <v>0.01634227888712348</v>
+        <v>0.03577</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>11.51743757540713</v>
+        <v>8.263845924855945</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2285,25 +2285,25 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.1080583303214745</v>
+        <v>0.1867360320017466</v>
       </c>
       <c r="C14">
-        <v>86.714976648575</v>
+        <v>55.40212464307618</v>
       </c>
       <c r="D14">
-        <v>98.07897664857501</v>
+        <v>62.63812464307617</v>
       </c>
       <c r="E14">
-        <v>11.364</v>
+        <v>7.236</v>
       </c>
       <c r="F14">
-        <v>11.364</v>
+        <v>7.236</v>
       </c>
       <c r="G14">
         <v>0</v>
       </c>
       <c r="H14">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2318,45 +2318,45 @@
         <v>2.801</v>
       </c>
       <c r="M14">
-        <v>0.2653052246761017</v>
+        <v>0.383508</v>
       </c>
       <c r="N14">
-        <v>2.535694775323898</v>
+        <v>2.417492</v>
       </c>
       <c r="O14">
-        <v>0.7607084325971695</v>
+        <v>0.7252476000000002</v>
       </c>
       <c r="P14">
-        <v>1.774986342726729</v>
+        <v>1.6922444</v>
       </c>
       <c r="Q14">
-        <v>2.173986342726729</v>
+        <v>2.0912444</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1205650646079769</v>
+        <v>0.2071409454565302</v>
       </c>
       <c r="T14">
-        <v>1.116954414247714</v>
+        <v>1.092555270162445</v>
       </c>
       <c r="U14">
-        <v>0.02334611269589068</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.01634227888712348</v>
+        <v>0.0371</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.55765111078986</v>
+        <v>7.303628607486676</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2367,25 +2367,25 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1079695266860392</v>
+        <v>0.1862580153046457</v>
       </c>
       <c r="C15">
-        <v>85.86176166069862</v>
+        <v>55.00217952207083</v>
       </c>
       <c r="D15">
-        <v>98.17276166069861</v>
+        <v>62.84117952207082</v>
       </c>
       <c r="E15">
-        <v>12.311</v>
+        <v>7.839</v>
       </c>
       <c r="F15">
-        <v>12.311</v>
+        <v>7.839</v>
       </c>
       <c r="G15">
         <v>0</v>
       </c>
       <c r="H15">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -2400,45 +2400,45 @@
         <v>2.801</v>
       </c>
       <c r="M15">
-        <v>0.3127934667488883</v>
+        <v>0.415467</v>
       </c>
       <c r="N15">
-        <v>2.488206533251112</v>
+        <v>2.385533</v>
       </c>
       <c r="O15">
-        <v>0.7464619599753335</v>
+        <v>0.7156599000000001</v>
       </c>
       <c r="P15">
-        <v>1.741744573275778</v>
+        <v>1.6698731</v>
       </c>
       <c r="Q15">
-        <v>2.140744573275778</v>
+        <v>2.0688731</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1214453234102087</v>
+        <v>0.2085459946030411</v>
       </c>
       <c r="T15">
-        <v>1.126277017504896</v>
+        <v>1.101674227203435</v>
       </c>
       <c r="U15">
-        <v>0.0254076408698634</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V15">
         <v>0.3</v>
       </c>
       <c r="W15">
-        <v>0.01778534860890438</v>
+        <v>0.0371</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y15">
-        <v>8.9547906134774</v>
+        <v>6.741811022295392</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2449,25 +2449,25 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1077075546839902</v>
+        <v>0.1857799986075448</v>
       </c>
       <c r="C16">
-        <v>85.19247674567946</v>
+        <v>54.60355517427961</v>
       </c>
       <c r="D16">
-        <v>98.45047674567945</v>
+        <v>63.04555517427961</v>
       </c>
       <c r="E16">
-        <v>13.258</v>
+        <v>8.442</v>
       </c>
       <c r="F16">
-        <v>13.258</v>
+        <v>8.442</v>
       </c>
       <c r="G16">
         <v>0</v>
       </c>
       <c r="H16">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -2482,45 +2482,45 @@
         <v>2.801</v>
       </c>
       <c r="M16">
-        <v>0.336854502652649</v>
+        <v>0.447426</v>
       </c>
       <c r="N16">
-        <v>2.464145497347351</v>
+        <v>2.353574</v>
       </c>
       <c r="O16">
-        <v>0.7392436492042053</v>
+        <v>0.7060722000000001</v>
       </c>
       <c r="P16">
-        <v>1.724901848143146</v>
+        <v>1.6475018</v>
       </c>
       <c r="Q16">
-        <v>2.123901848143146</v>
+        <v>2.0465018</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1223460533473763</v>
+        <v>0.2099837193110987</v>
       </c>
       <c r="T16">
-        <v>1.13581642548899</v>
+        <v>1.111005253012819</v>
       </c>
       <c r="U16">
-        <v>0.0254076408698634</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="V16">
         <v>0.3</v>
       </c>
       <c r="W16">
-        <v>0.01778534860890438</v>
+        <v>0.0371</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>8.315162712514727</v>
+        <v>6.260253092131435</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2531,25 +2531,25 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1075581421202401</v>
+        <v>0.185511981910444</v>
       </c>
       <c r="C17">
-        <v>84.40457293554081</v>
+        <v>54.11572819044824</v>
       </c>
       <c r="D17">
-        <v>98.60957293554081</v>
+        <v>63.16072819044824</v>
       </c>
       <c r="E17">
-        <v>14.205</v>
+        <v>9.045</v>
       </c>
       <c r="F17">
-        <v>14.205</v>
+        <v>9.045</v>
       </c>
       <c r="G17">
         <v>0</v>
       </c>
       <c r="H17">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -2564,45 +2564,45 @@
         <v>2.801</v>
       </c>
       <c r="M17">
-        <v>0.3761432225662749</v>
+        <v>0.497475</v>
       </c>
       <c r="N17">
-        <v>2.424856777433726</v>
+        <v>2.303525</v>
       </c>
       <c r="O17">
-        <v>0.7274570332301177</v>
+        <v>0.6910575000000001</v>
       </c>
       <c r="P17">
-        <v>1.697399744203608</v>
+        <v>1.6124675</v>
       </c>
       <c r="Q17">
-        <v>2.096399744203608</v>
+        <v>2.0114675</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1232679769301242</v>
+        <v>0.2114552728358164</v>
       </c>
       <c r="T17">
-        <v>1.145580290131534</v>
+        <v>1.12055583237066</v>
       </c>
       <c r="U17">
-        <v>0.0264796355203291</v>
+        <v>0.055</v>
       </c>
       <c r="V17">
         <v>0.3</v>
       </c>
       <c r="W17">
-        <v>0.01853574486423037</v>
+        <v>0.0385</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.446631580624787</v>
+        <v>5.630433690135183</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2613,25 +2613,25 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1073036740807444</v>
+        <v>0.1850479652133431</v>
       </c>
       <c r="C18">
-        <v>83.72972027620364</v>
+        <v>53.71312504683296</v>
       </c>
       <c r="D18">
-        <v>98.88172027620364</v>
+        <v>63.36112504683296</v>
       </c>
       <c r="E18">
-        <v>15.152</v>
+        <v>9.648</v>
       </c>
       <c r="F18">
-        <v>15.152</v>
+        <v>9.648</v>
       </c>
       <c r="G18">
         <v>0</v>
       </c>
       <c r="H18">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -2646,45 +2646,45 @@
         <v>2.801</v>
       </c>
       <c r="M18">
-        <v>0.4012194374040265</v>
+        <v>0.53064</v>
       </c>
       <c r="N18">
-        <v>2.399780562595974</v>
+        <v>2.27036</v>
       </c>
       <c r="O18">
-        <v>0.719934168778792</v>
+        <v>0.6811080000000002</v>
       </c>
       <c r="P18">
-        <v>1.679846393817181</v>
+        <v>1.589252</v>
       </c>
       <c r="Q18">
-        <v>2.078846393817182</v>
+        <v>1.988252</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1242118510743661</v>
+        <v>0.212961863349218</v>
       </c>
       <c r="T18">
-        <v>1.155576627741756</v>
+        <v>1.130333806475116</v>
       </c>
       <c r="U18">
-        <v>0.0264796355203291</v>
+        <v>0.055</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.01853574486423037</v>
+        <v>0.0385</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>6.981217106835737</v>
+        <v>5.278531584501734</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2695,25 +2695,25 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1070492060412487</v>
+        <v>0.1845839485162422</v>
       </c>
       <c r="C19">
-        <v>83.05637394417944</v>
+        <v>53.31179759218558</v>
       </c>
       <c r="D19">
-        <v>99.15537394417944</v>
+        <v>63.56279759218558</v>
       </c>
       <c r="E19">
-        <v>16.099</v>
+        <v>10.251</v>
       </c>
       <c r="F19">
-        <v>16.099</v>
+        <v>10.251</v>
       </c>
       <c r="G19">
         <v>0</v>
       </c>
       <c r="H19">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -2728,45 +2728,45 @@
         <v>2.801</v>
       </c>
       <c r="M19">
-        <v>0.4262956522417782</v>
+        <v>0.563805</v>
       </c>
       <c r="N19">
-        <v>2.374704347758222</v>
+        <v>2.237195</v>
       </c>
       <c r="O19">
-        <v>0.7124113043274666</v>
+        <v>0.6711585000000002</v>
       </c>
       <c r="P19">
-        <v>1.662293043430755</v>
+        <v>1.5660365</v>
       </c>
       <c r="Q19">
-        <v>2.061293043430755</v>
+        <v>1.9650365</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.125178469173891</v>
+        <v>0.2145047572484846</v>
       </c>
       <c r="T19">
-        <v>1.165813840957045</v>
+        <v>1.140347394413415</v>
       </c>
       <c r="U19">
-        <v>0.0264796355203291</v>
+        <v>0.055</v>
       </c>
       <c r="V19">
         <v>0.3</v>
       </c>
       <c r="W19">
-        <v>0.01853574486423037</v>
+        <v>0.0385</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.57055727702187</v>
+        <v>4.968029726589867</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2777,25 +2777,25 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1069817598376958</v>
+        <v>0.1841199318191414</v>
       </c>
       <c r="C20">
-        <v>82.18215937565375</v>
+        <v>52.91175804659816</v>
       </c>
       <c r="D20">
-        <v>99.22815937565375</v>
+        <v>63.76575804659816</v>
       </c>
       <c r="E20">
-        <v>17.046</v>
+        <v>10.854</v>
       </c>
       <c r="F20">
-        <v>17.046</v>
+        <v>10.854</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -2810,37 +2810,37 @@
         <v>2.801</v>
       </c>
       <c r="M20">
-        <v>0.4766732497420786</v>
+        <v>0.59697</v>
       </c>
       <c r="N20">
-        <v>2.324326750257922</v>
+        <v>2.20403</v>
       </c>
       <c r="O20">
-        <v>0.6972980250773765</v>
+        <v>0.6612090000000002</v>
       </c>
       <c r="P20">
-        <v>1.627028725180545</v>
+        <v>1.542821</v>
       </c>
       <c r="Q20">
-        <v>2.026028725180545</v>
+        <v>1.941821</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1261686633246237</v>
+        <v>0.2160852827062699</v>
       </c>
       <c r="T20">
-        <v>1.176300742299535</v>
+        <v>1.150605216203866</v>
       </c>
       <c r="U20">
-        <v>0.0279639358055895</v>
+        <v>0.055</v>
       </c>
       <c r="V20">
         <v>0.3</v>
       </c>
       <c r="W20">
-        <v>0.01957475506391265</v>
+        <v>0.0385</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.876142622888075</v>
+        <v>4.692028075112653</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2859,25 +2859,25 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1067376819001968</v>
+        <v>0.1841613151220405</v>
       </c>
       <c r="C21">
-        <v>81.49945463040061</v>
+        <v>52.29060440181571</v>
       </c>
       <c r="D21">
-        <v>99.4924546304006</v>
+        <v>63.74760440181571</v>
       </c>
       <c r="E21">
-        <v>17.993</v>
+        <v>11.457</v>
       </c>
       <c r="F21">
-        <v>17.993</v>
+        <v>11.457</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2892,45 +2892,45 @@
         <v>2.801</v>
       </c>
       <c r="M21">
-        <v>0.503155096949972</v>
+        <v>0.6736716</v>
       </c>
       <c r="N21">
-        <v>2.297844903050028</v>
+        <v>2.1273284</v>
       </c>
       <c r="O21">
-        <v>0.6893534709150084</v>
+        <v>0.6381985200000001</v>
       </c>
       <c r="P21">
-        <v>1.60849143213502</v>
+        <v>1.48912988</v>
       </c>
       <c r="Q21">
-        <v>2.00749143213502</v>
+        <v>1.88812988</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1271833067136462</v>
+        <v>0.2177048334840006</v>
       </c>
       <c r="T21">
-        <v>1.187046579477643</v>
+        <v>1.1611163175447</v>
       </c>
       <c r="U21">
-        <v>0.0279639358055895</v>
+        <v>0.05880000000000001</v>
       </c>
       <c r="V21">
         <v>0.3</v>
       </c>
       <c r="W21">
-        <v>0.01957475506391265</v>
+        <v>0.04116</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>5.566871958525543</v>
+        <v>4.157812204047195</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -2941,25 +2941,25 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1064936039626979</v>
+        <v>0.1843118984249396</v>
       </c>
       <c r="C22">
-        <v>80.81816155156331</v>
+        <v>51.62163505548293</v>
       </c>
       <c r="D22">
-        <v>99.7581615515633</v>
+        <v>63.68163505548294</v>
       </c>
       <c r="E22">
-        <v>18.94</v>
+        <v>12.06</v>
       </c>
       <c r="F22">
-        <v>18.94</v>
+        <v>12.06</v>
       </c>
       <c r="G22">
         <v>0</v>
       </c>
       <c r="H22">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2974,45 +2974,45 @@
         <v>2.801</v>
       </c>
       <c r="M22">
-        <v>0.5296369441578652</v>
+        <v>0.75978</v>
       </c>
       <c r="N22">
-        <v>2.271363055842135</v>
+        <v>2.04122</v>
       </c>
       <c r="O22">
-        <v>0.6814089167526405</v>
+        <v>0.6123660000000001</v>
       </c>
       <c r="P22">
-        <v>1.589954139089494</v>
+        <v>1.428854</v>
       </c>
       <c r="Q22">
-        <v>1.988954139089494</v>
+        <v>1.827854</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1282233161873943</v>
+        <v>0.2193648730311746</v>
       </c>
       <c r="T22">
-        <v>1.198061062585203</v>
+        <v>1.171890196419054</v>
       </c>
       <c r="U22">
-        <v>0.0279639358055895</v>
+        <v>0.063</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.01957475506391265</v>
+        <v>0.0441</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>5.288528360599266</v>
+        <v>3.686593487588512</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3023,25 +3023,25 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.106249526025199</v>
+        <v>0.1839038817278388</v>
       </c>
       <c r="C23">
-        <v>80.13829147951769</v>
+        <v>51.19770104663305</v>
       </c>
       <c r="D23">
-        <v>100.0252914795177</v>
+        <v>63.86070104663305</v>
       </c>
       <c r="E23">
-        <v>19.887</v>
+        <v>12.663</v>
       </c>
       <c r="F23">
-        <v>19.887</v>
+        <v>12.663</v>
       </c>
       <c r="G23">
         <v>0</v>
       </c>
       <c r="H23">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -3056,45 +3056,45 @@
         <v>2.801</v>
       </c>
       <c r="M23">
-        <v>0.5561187913657584</v>
+        <v>0.797769</v>
       </c>
       <c r="N23">
-        <v>2.244881208634242</v>
+        <v>2.003231</v>
       </c>
       <c r="O23">
-        <v>0.6734643625902725</v>
+        <v>0.6009693000000003</v>
       </c>
       <c r="P23">
-        <v>1.571416846043969</v>
+        <v>1.4022617</v>
       </c>
       <c r="Q23">
-        <v>1.970416846043969</v>
+        <v>1.8012617</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1292896550149081</v>
+        <v>0.2210669388959984</v>
       </c>
       <c r="T23">
-        <v>1.209354393366372</v>
+        <v>1.182936831720607</v>
       </c>
       <c r="U23">
-        <v>0.0279639358055895</v>
+        <v>0.063</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.01957475506391265</v>
+        <v>0.0441</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>5.036693676761207</v>
+        <v>3.511041416750965</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3105,25 +3105,25 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1060054480877001</v>
+        <v>0.1845892650307379</v>
       </c>
       <c r="C24">
-        <v>79.45985587643362</v>
+        <v>50.29447964007359</v>
       </c>
       <c r="D24">
-        <v>100.2938558764336</v>
+        <v>63.56047964007359</v>
       </c>
       <c r="E24">
-        <v>20.834</v>
+        <v>13.266</v>
       </c>
       <c r="F24">
-        <v>20.834</v>
+        <v>13.266</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -3138,45 +3138,45 @@
         <v>2.801</v>
       </c>
       <c r="M24">
-        <v>0.5826006385736516</v>
+        <v>0.9299466</v>
       </c>
       <c r="N24">
-        <v>2.218399361426349</v>
+        <v>1.8710534</v>
       </c>
       <c r="O24">
-        <v>0.6655198084279046</v>
+        <v>0.5613160200000001</v>
       </c>
       <c r="P24">
-        <v>1.552879552998444</v>
+        <v>1.30973738</v>
       </c>
       <c r="Q24">
-        <v>1.951879552998444</v>
+        <v>1.70873738</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1303833358636402</v>
+        <v>0.222812647475305</v>
       </c>
       <c r="T24">
-        <v>1.220937296731675</v>
+        <v>1.194266714081175</v>
       </c>
       <c r="U24">
-        <v>0.0279639358055895</v>
+        <v>0.0701</v>
       </c>
       <c r="V24">
         <v>0.3</v>
       </c>
       <c r="W24">
-        <v>0.01957475506391265</v>
+        <v>0.04907</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>4.807753055090243</v>
+        <v>3.012000904137937</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3187,25 +3187,25 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1057613701502012</v>
+        <v>0.187660248333637</v>
       </c>
       <c r="C25">
-        <v>78.7828663279145</v>
+        <v>48.38022849086524</v>
       </c>
       <c r="D25">
-        <v>100.5638663279145</v>
+        <v>62.24922849086524</v>
       </c>
       <c r="E25">
-        <v>21.781</v>
+        <v>13.869</v>
       </c>
       <c r="F25">
-        <v>21.781</v>
+        <v>13.869</v>
       </c>
       <c r="G25">
         <v>0</v>
       </c>
       <c r="H25">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -3220,45 +3220,45 @@
         <v>2.801</v>
       </c>
       <c r="M25">
-        <v>0.609082485781545</v>
+        <v>1.2676266</v>
       </c>
       <c r="N25">
-        <v>2.191917514218455</v>
+        <v>1.5333734</v>
       </c>
       <c r="O25">
-        <v>0.6575752542655365</v>
+        <v>0.4600120200000001</v>
       </c>
       <c r="P25">
-        <v>1.534342259952918</v>
+        <v>1.07336138</v>
       </c>
       <c r="Q25">
-        <v>1.933342259952918</v>
+        <v>1.47236138</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1315054240071446</v>
+        <v>0.2246036991345935</v>
       </c>
       <c r="T25">
-        <v>1.232821054729841</v>
+        <v>1.205890879100458</v>
       </c>
       <c r="U25">
-        <v>0.0279639358055895</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V25">
         <v>0.3</v>
       </c>
       <c r="W25">
-        <v>0.01957475506391265</v>
+        <v>0.06398000000000001</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.598720313564579</v>
+        <v>2.209641230311829</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3269,25 +3269,25 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1066055084115344</v>
+        <v>0.1874510316365361</v>
       </c>
       <c r="C26">
-        <v>76.90816472012492</v>
+        <v>47.86484024732972</v>
       </c>
       <c r="D26">
-        <v>99.63616472012492</v>
+        <v>62.33684024732972</v>
       </c>
       <c r="E26">
-        <v>22.728</v>
+        <v>14.472</v>
       </c>
       <c r="F26">
-        <v>22.728</v>
+        <v>14.472</v>
       </c>
       <c r="G26">
         <v>0</v>
       </c>
       <c r="H26">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -3302,45 +3302,45 @@
         <v>2.801</v>
       </c>
       <c r="M26">
-        <v>0.7827844387457148</v>
+        <v>1.3227408</v>
       </c>
       <c r="N26">
-        <v>2.018215561254285</v>
+        <v>1.4782592</v>
       </c>
       <c r="O26">
-        <v>0.6054646683762855</v>
+        <v>0.4434777600000001</v>
       </c>
       <c r="P26">
-        <v>1.412750892878</v>
+        <v>1.03478144</v>
       </c>
       <c r="Q26">
-        <v>1.811750892878</v>
+        <v>1.43378144</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1326570407860043</v>
+        <v>0.2264418837322844</v>
       </c>
       <c r="T26">
-        <v>1.245017543201645</v>
+        <v>1.217820943199196</v>
       </c>
       <c r="U26">
-        <v>0.0344414131795897</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V26">
         <v>0.3</v>
       </c>
       <c r="W26">
-        <v>0.02410898922571279</v>
+        <v>0.06398000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.578252021064891</v>
+        <v>2.117572845715502</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3351,25 +3351,25 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1067891060328873</v>
+        <v>0.1872418149394353</v>
       </c>
       <c r="C27">
-        <v>75.76165396432393</v>
+        <v>47.34969896712219</v>
       </c>
       <c r="D27">
-        <v>99.43665396432392</v>
+        <v>62.42469896712219</v>
       </c>
       <c r="E27">
-        <v>23.675</v>
+        <v>15.075</v>
       </c>
       <c r="F27">
-        <v>23.675</v>
+        <v>15.075</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -3384,45 +3384,45 @@
         <v>2.801</v>
       </c>
       <c r="M27">
-        <v>0.867124679415416</v>
+        <v>1.377855</v>
       </c>
       <c r="N27">
-        <v>1.933875320584584</v>
+        <v>1.423145</v>
       </c>
       <c r="O27">
-        <v>0.5801625961753752</v>
+        <v>0.4269435000000001</v>
       </c>
       <c r="P27">
-        <v>1.353712724409209</v>
+        <v>0.9962015</v>
       </c>
       <c r="Q27">
-        <v>1.752712724409209</v>
+        <v>1.3952015</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1338393673456337</v>
+        <v>0.2283290865859137</v>
       </c>
       <c r="T27">
-        <v>1.257539271366029</v>
+        <v>1.230069142340568</v>
       </c>
       <c r="U27">
-        <v>0.0366261744209257</v>
+        <v>0.09140000000000001</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.02563832209464799</v>
+        <v>0.06398000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>3.230215984497561</v>
+        <v>2.032869931886882</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3433,25 +3433,25 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1066056637656957</v>
+        <v>0.1908727982423344</v>
       </c>
       <c r="C28">
-        <v>75.01399556236821</v>
+        <v>45.25620860817629</v>
       </c>
       <c r="D28">
-        <v>99.63599556236821</v>
+        <v>60.93420860817629</v>
       </c>
       <c r="E28">
-        <v>24.622</v>
+        <v>15.678</v>
       </c>
       <c r="F28">
-        <v>24.622</v>
+        <v>15.678</v>
       </c>
       <c r="G28">
         <v>0</v>
       </c>
       <c r="H28">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -3466,45 +3466,45 @@
         <v>2.801</v>
       </c>
       <c r="M28">
-        <v>0.9018096665920327</v>
+        <v>1.763775</v>
       </c>
       <c r="N28">
-        <v>1.899190333407967</v>
+        <v>1.037225</v>
       </c>
       <c r="O28">
-        <v>0.5697571000223902</v>
+        <v>0.3111675000000002</v>
       </c>
       <c r="P28">
-        <v>1.329433233385577</v>
+        <v>0.7260575000000001</v>
       </c>
       <c r="Q28">
-        <v>1.728433233385577</v>
+        <v>1.1250575</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1350536486771449</v>
+        <v>0.2302672949220735</v>
       </c>
       <c r="T28">
-        <v>1.270399424615937</v>
+        <v>1.242648373891165</v>
       </c>
       <c r="U28">
-        <v>0.0366261744209257</v>
+        <v>0.1125</v>
       </c>
       <c r="V28">
         <v>0.3</v>
       </c>
       <c r="W28">
-        <v>0.02563832209464799</v>
+        <v>0.07875</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>3.105976908170732</v>
+        <v>1.58807104080736</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3515,25 +3515,25 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1094917750410399</v>
+        <v>0.1908112815452335</v>
       </c>
       <c r="C29">
-        <v>71.02053764696548</v>
+        <v>44.67786777304831</v>
       </c>
       <c r="D29">
-        <v>96.58953764696548</v>
+        <v>60.95886777304831</v>
       </c>
       <c r="E29">
-        <v>25.569</v>
+        <v>16.281</v>
       </c>
       <c r="F29">
-        <v>25.569</v>
+        <v>16.281</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -3548,45 +3548,45 @@
         <v>2.801</v>
       </c>
       <c r="M29">
-        <v>1.35176139730883</v>
+        <v>1.8316125</v>
       </c>
       <c r="N29">
-        <v>1.44923860269117</v>
+        <v>0.9693875000000003</v>
       </c>
       <c r="O29">
-        <v>0.4347715808073509</v>
+        <v>0.2908162500000001</v>
       </c>
       <c r="P29">
-        <v>1.014467021883819</v>
+        <v>0.6785712500000002</v>
       </c>
       <c r="Q29">
-        <v>1.413467021883819</v>
+        <v>1.07757125</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1363011979903414</v>
+        <v>0.2322586048564843</v>
       </c>
       <c r="T29">
-        <v>1.283611910831596</v>
+        <v>1.255572241922601</v>
       </c>
       <c r="U29">
-        <v>0.0528671984555059</v>
+        <v>0.1125</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03700703891885413</v>
+        <v>0.07875</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y29">
-        <v>2.072111250976986</v>
+        <v>1.529253594851531</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3597,25 +3597,25 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1110669912525969</v>
+        <v>0.2118283746347674</v>
       </c>
       <c r="C30">
-        <v>68.4881028679609</v>
+        <v>36.67042788668236</v>
       </c>
       <c r="D30">
-        <v>95.00410286796091</v>
+        <v>53.55442788668236</v>
       </c>
       <c r="E30">
-        <v>26.516</v>
+        <v>16.884</v>
       </c>
       <c r="F30">
-        <v>26.516</v>
+        <v>16.884</v>
       </c>
       <c r="G30">
         <v>0</v>
       </c>
       <c r="H30">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -3630,45 +3630,45 @@
         <v>2.801</v>
       </c>
       <c r="M30">
-        <v>1.624367752967574</v>
+        <v>3.3193944</v>
       </c>
       <c r="N30">
-        <v>1.176632247032426</v>
+        <v>-0.5183944</v>
       </c>
       <c r="O30">
-        <v>0.3529896741097279</v>
+        <v>-0.15551832</v>
       </c>
       <c r="P30">
-        <v>0.8236425729226984</v>
+        <v>-0.36287608</v>
       </c>
       <c r="Q30">
-        <v>1.222642572922698</v>
+        <v>0.03612392000000003</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1375834014511267</v>
+        <v>0.2371051361359055</v>
       </c>
       <c r="T30">
-        <v>1.297191410553246</v>
+        <v>1.287026878683603</v>
       </c>
       <c r="U30">
-        <v>0.06125990922339621</v>
+        <v>0.1966</v>
       </c>
       <c r="V30">
-        <v>0.3</v>
+        <v>0.2531485863806964</v>
       </c>
       <c r="W30">
-        <v>0.04288193645637734</v>
+        <v>0.1468309879175551</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y30">
-        <v>1.724363214477032</v>
+        <v>0.8438286212689881</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3679,25 +3679,25 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1110559851290226</v>
+        <v>0.2134063746347674</v>
       </c>
       <c r="C31">
-        <v>67.55199981091681</v>
+        <v>35.58343131220474</v>
       </c>
       <c r="D31">
-        <v>95.01499981091681</v>
+        <v>53.07043131220474</v>
       </c>
       <c r="E31">
-        <v>27.463</v>
+        <v>17.487</v>
       </c>
       <c r="F31">
-        <v>27.463</v>
+        <v>17.487</v>
       </c>
       <c r="G31">
         <v>0</v>
       </c>
       <c r="H31">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -3712,45 +3712,45 @@
         <v>2.801</v>
       </c>
       <c r="M31">
-        <v>1.68238088700213</v>
+        <v>3.4379442</v>
       </c>
       <c r="N31">
-        <v>1.11861911299787</v>
+        <v>-0.6369441999999994</v>
       </c>
       <c r="O31">
-        <v>0.3355857338993611</v>
+        <v>-0.1910832599999998</v>
       </c>
       <c r="P31">
-        <v>0.7830333790985093</v>
+        <v>-0.4458609399999995</v>
       </c>
       <c r="Q31">
-        <v>1.182033379098509</v>
+        <v>-0.04686093999999952</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.138901723319258</v>
+        <v>0.2398981662223267</v>
       </c>
       <c r="T31">
-        <v>1.311153431393815</v>
+        <v>1.305154017819992</v>
       </c>
       <c r="U31">
-        <v>0.06125990922339621</v>
+        <v>0.1966</v>
       </c>
       <c r="V31">
-        <v>0.3</v>
+        <v>0.2444193247813622</v>
       </c>
       <c r="W31">
-        <v>0.04288193645637734</v>
+        <v>0.1485471607479842</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y31">
-        <v>1.664902413977825</v>
+        <v>0.8147310826045404</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3761,25 +3761,25 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.1110449790054483</v>
+        <v>0.2210206683242183</v>
       </c>
       <c r="C32">
-        <v>66.61589925391181</v>
+        <v>32.76282419906448</v>
       </c>
       <c r="D32">
-        <v>95.0258992539118</v>
+        <v>50.85282419906448</v>
       </c>
       <c r="E32">
-        <v>28.41</v>
+        <v>18.09</v>
       </c>
       <c r="F32">
-        <v>28.41</v>
+        <v>18.09</v>
       </c>
       <c r="G32">
         <v>0</v>
       </c>
       <c r="H32">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -3794,45 +3794,45 @@
         <v>2.801</v>
       </c>
       <c r="M32">
-        <v>1.740394021036686</v>
+        <v>3.867642</v>
       </c>
       <c r="N32">
-        <v>1.060605978963314</v>
+        <v>-1.066641999999999</v>
       </c>
       <c r="O32">
-        <v>0.3181817936889942</v>
+        <v>-0.3199925999999998</v>
       </c>
       <c r="P32">
-        <v>0.7424241852743199</v>
+        <v>-0.7466493999999996</v>
       </c>
       <c r="Q32">
-        <v>1.14142418527432</v>
+        <v>-0.3476493999999996</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1402577115264788</v>
+        <v>0.244022845296147</v>
       </c>
       <c r="T32">
-        <v>1.325514367115544</v>
+        <v>1.331923737139376</v>
       </c>
       <c r="U32">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V32">
-        <v>0.3</v>
+        <v>0.2172641625052164</v>
       </c>
       <c r="W32">
-        <v>0.04288193645637734</v>
+        <v>0.1673489220563847</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>1.609405666845231</v>
+        <v>0.724213875017388</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3843,25 +3843,25 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1110339728818741</v>
+        <v>0.2227706683242183</v>
       </c>
       <c r="C33">
-        <v>65.67980119780638</v>
+        <v>31.67609250879563</v>
       </c>
       <c r="D33">
-        <v>95.03680119780638</v>
+        <v>50.36909250879563</v>
       </c>
       <c r="E33">
-        <v>29.357</v>
+        <v>18.693</v>
       </c>
       <c r="F33">
-        <v>29.357</v>
+        <v>18.693</v>
       </c>
       <c r="G33">
         <v>0</v>
       </c>
       <c r="H33">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -3876,45 +3876,45 @@
         <v>2.801</v>
       </c>
       <c r="M33">
-        <v>1.798407155071242</v>
+        <v>3.996563399999999</v>
       </c>
       <c r="N33">
-        <v>1.002592844928758</v>
+        <v>-1.195563399999999</v>
       </c>
       <c r="O33">
-        <v>0.3007778534786273</v>
+        <v>-0.3586690199999998</v>
       </c>
       <c r="P33">
-        <v>0.7018149914501304</v>
+        <v>-0.8368943799999995</v>
       </c>
       <c r="Q33">
-        <v>1.10081499145013</v>
+        <v>-0.4378943799999995</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.141653003739706</v>
+        <v>0.2469970894308738</v>
       </c>
       <c r="T33">
-        <v>1.340291561843699</v>
+        <v>1.351226979706613</v>
       </c>
       <c r="U33">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V33">
-        <v>0.3</v>
+        <v>0.2102556411340804</v>
       </c>
       <c r="W33">
-        <v>0.04288193645637734</v>
+        <v>0.1688473439255336</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y33">
-        <v>1.557489355011513</v>
+        <v>0.7008521371136013</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -3925,25 +3925,25 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1110229667582998</v>
+        <v>0.2245206683242183</v>
       </c>
       <c r="C34">
-        <v>64.74370564346142</v>
+        <v>30.59847698707828</v>
       </c>
       <c r="D34">
-        <v>95.04770564346143</v>
+        <v>49.89447698707828</v>
       </c>
       <c r="E34">
-        <v>30.304</v>
+        <v>19.296</v>
       </c>
       <c r="F34">
-        <v>30.304</v>
+        <v>19.296</v>
       </c>
       <c r="G34">
         <v>0</v>
       </c>
       <c r="H34">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -3958,45 +3958,45 @@
         <v>2.801</v>
       </c>
       <c r="M34">
-        <v>1.856420289105799</v>
+        <v>4.1254848</v>
       </c>
       <c r="N34">
-        <v>0.9445797108942013</v>
+        <v>-1.3244848</v>
       </c>
       <c r="O34">
-        <v>0.2833739132682604</v>
+        <v>-0.3973454399999999</v>
       </c>
       <c r="P34">
-        <v>0.6612057976259409</v>
+        <v>-0.9271393599999996</v>
       </c>
       <c r="Q34">
-        <v>1.060205797625941</v>
+        <v>-0.5281393599999996</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1430893339592045</v>
+        <v>0.250058811334269</v>
       </c>
       <c r="T34">
-        <v>1.355503379946212</v>
+        <v>1.371097964702299</v>
       </c>
       <c r="U34">
-        <v>0.06125990922339621</v>
+        <v>0.2138</v>
       </c>
       <c r="V34">
-        <v>0.3</v>
+        <v>0.2036851523486404</v>
       </c>
       <c r="W34">
-        <v>0.04288193645637734</v>
+        <v>0.1702521144278607</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.508817812667403</v>
+        <v>0.6789505078288012</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4007,25 +4007,25 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1232559730691888</v>
+        <v>0.2262706683242183</v>
       </c>
       <c r="C35">
-        <v>53.04631294690476</v>
+        <v>29.52972234125614</v>
       </c>
       <c r="D35">
-        <v>84.29731294690477</v>
+        <v>49.42872234125614</v>
       </c>
       <c r="E35">
-        <v>31.251</v>
+        <v>19.899</v>
       </c>
       <c r="F35">
-        <v>31.251</v>
+        <v>19.899</v>
       </c>
       <c r="G35">
         <v>0</v>
       </c>
       <c r="H35">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -4040,45 +4040,45 @@
         <v>2.801</v>
       </c>
       <c r="M35">
-        <v>3.2219781</v>
+        <v>4.2544062</v>
       </c>
       <c r="N35">
-        <v>-0.4209780999999997</v>
+        <v>-1.4534062</v>
       </c>
       <c r="O35">
-        <v>-0.1262934299999999</v>
+        <v>-0.43602186</v>
       </c>
       <c r="P35">
-        <v>-0.2946846699999998</v>
+        <v>-1.01738434</v>
       </c>
       <c r="Q35">
-        <v>0.1043153300000003</v>
+        <v>-0.6183843399999998</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1464272494389539</v>
+        <v>0.2532119279213476</v>
       </c>
       <c r="T35">
-        <v>1.390854417214811</v>
+        <v>1.391562113429199</v>
       </c>
       <c r="U35">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V35">
-        <v>0.2608025175590113</v>
+        <v>0.1975128750047422</v>
       </c>
       <c r="W35">
-        <v>0.07621126043966592</v>
+        <v>0.1715717473239861</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y35">
-        <v>0.8693417251967046</v>
+        <v>0.6583762500158072</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4089,25 +4089,25 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1241359730691888</v>
+        <v>0.2280206683242183</v>
       </c>
       <c r="C36">
-        <v>51.41897201624509</v>
+        <v>28.46958272292975</v>
       </c>
       <c r="D36">
-        <v>83.61697201624509</v>
+        <v>48.97158272292975</v>
       </c>
       <c r="E36">
-        <v>32.198</v>
+        <v>20.502</v>
       </c>
       <c r="F36">
-        <v>32.198</v>
+        <v>20.502</v>
       </c>
       <c r="G36">
         <v>0</v>
       </c>
       <c r="H36">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -4122,45 +4122,45 @@
         <v>2.801</v>
       </c>
       <c r="M36">
-        <v>3.3196138</v>
+        <v>4.383327599999999</v>
       </c>
       <c r="N36">
-        <v>-0.5186137999999998</v>
+        <v>-1.582327599999999</v>
       </c>
       <c r="O36">
-        <v>-0.1555841399999999</v>
+        <v>-0.4746982799999999</v>
       </c>
       <c r="P36">
-        <v>-0.3630296599999999</v>
+        <v>-1.107629319999999</v>
       </c>
       <c r="Q36">
-        <v>0.03597034000000016</v>
+        <v>-0.7086293199999993</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.148417056248635</v>
+        <v>0.2564605934959134</v>
       </c>
       <c r="T36">
-        <v>1.411927968990793</v>
+        <v>1.412646387875095</v>
       </c>
       <c r="U36">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V36">
-        <v>0.253131855277864</v>
+        <v>0.1917036727987204</v>
       </c>
       <c r="W36">
-        <v>0.07700210572085223</v>
+        <v>0.1728137547556336</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y36">
-        <v>0.8437728509262132</v>
+        <v>0.6390122426624012</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4171,25 +4171,25 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1250159730691889</v>
+        <v>0.2297706683242182</v>
       </c>
       <c r="C37">
-        <v>49.80252486202685</v>
+        <v>27.41782129523434</v>
       </c>
       <c r="D37">
-        <v>82.94752486202685</v>
+        <v>48.52282129523434</v>
       </c>
       <c r="E37">
-        <v>33.145</v>
+        <v>21.105</v>
       </c>
       <c r="F37">
-        <v>33.145</v>
+        <v>21.105</v>
       </c>
       <c r="G37">
         <v>0</v>
       </c>
       <c r="H37">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -4204,45 +4204,45 @@
         <v>2.801</v>
       </c>
       <c r="M37">
-        <v>3.4172495</v>
+        <v>4.512249</v>
       </c>
       <c r="N37">
-        <v>-0.6162494999999999</v>
+        <v>-1.711249</v>
       </c>
       <c r="O37">
-        <v>-0.18487485</v>
+        <v>-0.5133747</v>
       </c>
       <c r="P37">
-        <v>-0.43137465</v>
+        <v>-1.1978743</v>
       </c>
       <c r="Q37">
-        <v>-0.03237464999999995</v>
+        <v>-0.7988742999999996</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1504680878832294</v>
+        <v>0.2598092180112351</v>
       </c>
       <c r="T37">
-        <v>1.433649937744498</v>
+        <v>1.43437940922702</v>
       </c>
       <c r="U37">
-        <v>0.1031</v>
+        <v>0.2138</v>
       </c>
       <c r="V37">
-        <v>0.2458995165556393</v>
+        <v>0.1862264250044712</v>
       </c>
       <c r="W37">
-        <v>0.07774775984311359</v>
+        <v>0.173984790334044</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.8196650551854643</v>
+        <v>0.620754750014904</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4253,25 +4253,25 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.1342564018431931</v>
+        <v>0.2315206683242183</v>
       </c>
       <c r="C38">
-        <v>42.42304885896526</v>
+        <v>26.37420982369351</v>
       </c>
       <c r="D38">
-        <v>76.51504885896526</v>
+        <v>48.08220982369351</v>
       </c>
       <c r="E38">
-        <v>34.092</v>
+        <v>21.708</v>
       </c>
       <c r="F38">
-        <v>34.092</v>
+        <v>21.708</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -4286,37 +4286,37 @@
         <v>2.801</v>
       </c>
       <c r="M38">
-        <v>4.181521474588889</v>
+        <v>4.641170399999999</v>
       </c>
       <c r="N38">
-        <v>-1.380521474588889</v>
+        <v>-1.840170399999999</v>
       </c>
       <c r="O38">
-        <v>-0.4141564423766667</v>
+        <v>-0.5520511199999998</v>
       </c>
       <c r="P38">
-        <v>-0.9663650322122224</v>
+        <v>-1.288119279999999</v>
       </c>
       <c r="Q38">
-        <v>-0.5673650322122223</v>
+        <v>-0.8891192799999992</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1546472376577596</v>
+        <v>0.2632624870426608</v>
       </c>
       <c r="T38">
-        <v>1.477910279363924</v>
+        <v>1.456791587496192</v>
       </c>
       <c r="U38">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V38">
-        <v>0.2009555624923856</v>
+        <v>0.181053468754347</v>
       </c>
       <c r="W38">
-        <v>0.09800602706174144</v>
+        <v>0.1750907683803206</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.6698518749746187</v>
+        <v>0.60351156251449</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4335,25 +4335,25 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.1353319422264469</v>
+        <v>0.2332706683242183</v>
       </c>
       <c r="C39">
-        <v>40.79157996117884</v>
+        <v>25.33852828916422</v>
       </c>
       <c r="D39">
-        <v>75.83057996117884</v>
+        <v>47.64952828916422</v>
       </c>
       <c r="E39">
-        <v>35.039</v>
+        <v>22.311</v>
       </c>
       <c r="F39">
-        <v>35.039</v>
+        <v>22.311</v>
       </c>
       <c r="G39">
         <v>0</v>
       </c>
       <c r="H39">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -4368,37 +4368,37 @@
         <v>2.801</v>
       </c>
       <c r="M39">
-        <v>4.297674848883025</v>
+        <v>4.770091799999999</v>
       </c>
       <c r="N39">
-        <v>-1.496674848883025</v>
+        <v>-1.969091799999999</v>
       </c>
       <c r="O39">
-        <v>-0.4490024546649075</v>
+        <v>-0.5907275399999998</v>
       </c>
       <c r="P39">
-        <v>-1.047672394218117</v>
+        <v>-1.378364259999999</v>
       </c>
       <c r="Q39">
-        <v>-0.6486723942181174</v>
+        <v>-0.9793642599999994</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1568622731761368</v>
+        <v>0.2668253836623855</v>
       </c>
       <c r="T39">
-        <v>1.501369172687161</v>
+        <v>1.479915263488195</v>
       </c>
       <c r="U39">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V39">
-        <v>0.1955243310736725</v>
+        <v>0.1761601317609863</v>
       </c>
       <c r="W39">
-        <v>0.09867218952832629</v>
+        <v>0.1761369638295011</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.651747770245575</v>
+        <v>0.5872004392032876</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4417,25 +4417,25 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.1364074826097007</v>
+        <v>0.2350206683242183</v>
       </c>
       <c r="C40">
-        <v>39.1722483845999</v>
+        <v>24.31056452149292</v>
       </c>
       <c r="D40">
-        <v>75.1582483845999</v>
+        <v>47.22456452149292</v>
       </c>
       <c r="E40">
-        <v>35.986</v>
+        <v>22.914</v>
       </c>
       <c r="F40">
-        <v>35.986</v>
+        <v>22.914</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -4450,37 +4450,37 @@
         <v>2.801</v>
       </c>
       <c r="M40">
-        <v>4.413828223177162</v>
+        <v>4.8990132</v>
       </c>
       <c r="N40">
-        <v>-1.612828223177162</v>
+        <v>-2.0980132</v>
       </c>
       <c r="O40">
-        <v>-0.4838484669531484</v>
+        <v>-0.62940396</v>
       </c>
       <c r="P40">
-        <v>-1.128979756224013</v>
+        <v>-1.46860924</v>
       </c>
       <c r="Q40">
-        <v>-0.7299797562240131</v>
+        <v>-1.06960924</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1591487614531712</v>
+        <v>0.2705032124311337</v>
       </c>
       <c r="T40">
-        <v>1.525584804504695</v>
+        <v>1.503784864512199</v>
       </c>
       <c r="U40">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V40">
-        <v>0.1903789539401548</v>
+        <v>0.1715243388199077</v>
       </c>
       <c r="W40">
-        <v>0.09930329081245931</v>
+        <v>0.1771280963603037</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4488,7 +4488,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.6345965131338492</v>
+        <v>0.5717477960663588</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4499,25 +4499,25 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.1374830229929545</v>
+        <v>0.2367706683242183</v>
       </c>
       <c r="C41">
-        <v>37.56473412947391</v>
+        <v>23.29011385260258</v>
       </c>
       <c r="D41">
-        <v>74.49773412947391</v>
+        <v>46.80711385260258</v>
       </c>
       <c r="E41">
-        <v>36.933</v>
+        <v>23.517</v>
       </c>
       <c r="F41">
-        <v>36.933</v>
+        <v>23.517</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -4532,37 +4532,37 @@
         <v>2.801</v>
       </c>
       <c r="M41">
-        <v>4.529981597471297</v>
+        <v>5.0279346</v>
       </c>
       <c r="N41">
-        <v>-1.728981597471297</v>
+        <v>-2.2269346</v>
       </c>
       <c r="O41">
-        <v>-0.5186944792413889</v>
+        <v>-0.66808038</v>
       </c>
       <c r="P41">
-        <v>-1.210287118229908</v>
+        <v>-1.55885422</v>
       </c>
       <c r="Q41">
-        <v>-0.8112871182299077</v>
+        <v>-1.15985422</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1615102165589609</v>
+        <v>0.2743016257496769</v>
       </c>
       <c r="T41">
-        <v>1.550594391463789</v>
+        <v>1.528437075405841</v>
       </c>
       <c r="U41">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V41">
-        <v>0.1854974423006636</v>
+        <v>0.1671262788501665</v>
       </c>
       <c r="W41">
-        <v>0.09990202792817525</v>
+        <v>0.1780684015818344</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.6183248076688789</v>
+        <v>0.5570875961672215</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4581,25 +4581,25 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.1385585633762083</v>
+        <v>0.2385206683242183</v>
       </c>
       <c r="C42">
-        <v>35.96872834708038</v>
+        <v>22.27697878781758</v>
       </c>
       <c r="D42">
-        <v>73.84872834708038</v>
+        <v>46.39697878781758</v>
       </c>
       <c r="E42">
-        <v>37.88</v>
+        <v>24.12</v>
       </c>
       <c r="F42">
-        <v>37.88</v>
+        <v>24.12</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -4614,37 +4614,37 @@
         <v>2.801</v>
       </c>
       <c r="M42">
-        <v>4.646134971765433</v>
+        <v>5.156856</v>
       </c>
       <c r="N42">
-        <v>-1.845134971765432</v>
+        <v>-2.355856</v>
       </c>
       <c r="O42">
-        <v>-0.5535404915296297</v>
+        <v>-0.7067568000000002</v>
       </c>
       <c r="P42">
-        <v>-1.291594480235803</v>
+        <v>-1.6490992</v>
       </c>
       <c r="Q42">
-        <v>-0.8925944802358026</v>
+        <v>-1.2500992</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1639503868349436</v>
+        <v>0.2782266528455049</v>
       </c>
       <c r="T42">
-        <v>1.576437631321519</v>
+        <v>1.553911026662605</v>
       </c>
       <c r="U42">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V42">
-        <v>0.180860006243147</v>
+        <v>0.1629481218789123</v>
       </c>
       <c r="W42">
-        <v>0.1004708281881054</v>
+        <v>0.1789616915422886</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.6028666874771569</v>
+        <v>0.5431604062630409</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4663,25 +4663,25 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.1396341037594621</v>
+        <v>0.2402706683242183</v>
       </c>
       <c r="C43">
-        <v>34.38393285820259</v>
+        <v>21.27096869431843</v>
       </c>
       <c r="D43">
-        <v>73.2109328582026</v>
+        <v>45.99396869431843</v>
       </c>
       <c r="E43">
-        <v>38.82700000000001</v>
+        <v>24.723</v>
       </c>
       <c r="F43">
-        <v>38.82700000000001</v>
+        <v>24.723</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -4696,37 +4696,37 @@
         <v>2.801</v>
       </c>
       <c r="M43">
-        <v>4.762288346059569</v>
+        <v>5.2857774</v>
       </c>
       <c r="N43">
-        <v>-1.961288346059569</v>
+        <v>-2.4847774</v>
       </c>
       <c r="O43">
-        <v>-0.5883865038178707</v>
+        <v>-0.74543322</v>
       </c>
       <c r="P43">
-        <v>-1.372901842241698</v>
+        <v>-1.73934418</v>
       </c>
       <c r="Q43">
-        <v>-0.9739018422416983</v>
+        <v>-1.34034418</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1664732747474003</v>
+        <v>0.282284731707293</v>
       </c>
       <c r="T43">
-        <v>1.603156913208324</v>
+        <v>1.580248501690785</v>
       </c>
       <c r="U43">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V43">
-        <v>0.17644878657868</v>
+        <v>0.1589737774428413</v>
       </c>
       <c r="W43">
-        <v>0.1010118820938926</v>
+        <v>0.1798114063827205</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5881626219289334</v>
+        <v>0.5299125914761376</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4745,25 +4745,25 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.1407096441427159</v>
+        <v>0.2420206683242183</v>
       </c>
       <c r="C44">
-        <v>32.81005969633603</v>
+        <v>20.27189950569317</v>
       </c>
       <c r="D44">
-        <v>72.58405969633603</v>
+        <v>45.59789950569316</v>
       </c>
       <c r="E44">
-        <v>39.774</v>
+        <v>25.326</v>
       </c>
       <c r="F44">
-        <v>39.774</v>
+        <v>25.326</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -4778,37 +4778,37 @@
         <v>2.801</v>
       </c>
       <c r="M44">
-        <v>4.878441720353704</v>
+        <v>5.414698799999999</v>
       </c>
       <c r="N44">
-        <v>-2.077441720353704</v>
+        <v>-2.613698799999999</v>
       </c>
       <c r="O44">
-        <v>-0.6232325161061112</v>
+        <v>-0.7841096399999998</v>
       </c>
       <c r="P44">
-        <v>-1.454209204247593</v>
+        <v>-1.829589159999999</v>
       </c>
       <c r="Q44">
-        <v>-1.055209204247593</v>
+        <v>-1.430589159999999</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1690831587947692</v>
+        <v>0.286482744322936</v>
       </c>
       <c r="T44">
-        <v>1.63079754964295</v>
+        <v>1.607494165513039</v>
       </c>
       <c r="U44">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V44">
-        <v>0.1722476249934734</v>
+        <v>0.155188687503726</v>
       </c>
       <c r="W44">
-        <v>0.1015271715279757</v>
+        <v>0.1806206586117034</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4816,7 +4816,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5741587499782446</v>
+        <v>0.51729562501242</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4827,25 +4827,25 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.1417851845259697</v>
+        <v>0.2437706683242183</v>
       </c>
       <c r="C45">
-        <v>31.24683067416561</v>
+        <v>19.27959344162383</v>
       </c>
       <c r="D45">
-        <v>71.96783067416561</v>
+        <v>45.20859344162383</v>
       </c>
       <c r="E45">
-        <v>40.721</v>
+        <v>25.929</v>
       </c>
       <c r="F45">
-        <v>40.721</v>
+        <v>25.929</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -4860,37 +4860,37 @@
         <v>2.801</v>
       </c>
       <c r="M45">
-        <v>4.99459509464784</v>
+        <v>5.543620199999999</v>
       </c>
       <c r="N45">
-        <v>-2.19359509464784</v>
+        <v>-2.742620199999999</v>
       </c>
       <c r="O45">
-        <v>-0.658078528394352</v>
+        <v>-0.8227860599999999</v>
       </c>
       <c r="P45">
-        <v>-1.535516566253488</v>
+        <v>-1.919834139999999</v>
       </c>
       <c r="Q45">
-        <v>-1.136516566253488</v>
+        <v>-1.520834139999999</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1717846177209932</v>
+        <v>0.2908280556268472</v>
       </c>
       <c r="T45">
-        <v>1.65940803297002</v>
+        <v>1.635695817539584</v>
       </c>
       <c r="U45">
-        <v>0.122654038325381</v>
+        <v>0.2138</v>
       </c>
       <c r="V45">
-        <v>0.1682418662726949</v>
+        <v>0.1515796482594533</v>
       </c>
       <c r="W45">
-        <v>0.1020184940116362</v>
+        <v>0.1813922712021289</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5608062209089831</v>
+        <v>0.5052654941981777</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4909,25 +4909,25 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.1428607249092236</v>
+        <v>0.2575692697333111</v>
       </c>
       <c r="C46">
-        <v>29.69397697194034</v>
+        <v>15.82511726342408</v>
       </c>
       <c r="D46">
-        <v>71.36197697194034</v>
+        <v>42.35711726342408</v>
       </c>
       <c r="E46">
-        <v>41.668</v>
+        <v>26.532</v>
       </c>
       <c r="F46">
-        <v>41.668</v>
+        <v>26.532</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -4942,45 +4942,45 @@
         <v>2.801</v>
       </c>
       <c r="M46">
-        <v>5.110748468941976</v>
+        <v>6.3358416</v>
       </c>
       <c r="N46">
-        <v>-2.309748468941976</v>
+        <v>-3.5348416</v>
       </c>
       <c r="O46">
-        <v>-0.6929245406825927</v>
+        <v>-1.06045248</v>
       </c>
       <c r="P46">
-        <v>-1.616823928259383</v>
+        <v>-2.47438912</v>
       </c>
       <c r="Q46">
-        <v>-1.217823928259383</v>
+        <v>-2.07538912</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1745825573231538</v>
+        <v>0.2972010591364208</v>
       </c>
       <c r="T46">
-        <v>1.689040319273056</v>
+        <v>1.677057463408126</v>
       </c>
       <c r="U46">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V46">
-        <v>0.16441818749377</v>
+        <v>0.1326264217211491</v>
       </c>
       <c r="W46">
-        <v>0.1024874836551305</v>
+        <v>0.2071288104929896</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y46">
-        <v>0.5480606249792335</v>
+        <v>0.4420880724038303</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -4991,25 +4991,25 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.1439362652924774</v>
+        <v>0.2595692697333111</v>
       </c>
       <c r="C47">
-        <v>28.15123874646547</v>
+        <v>14.83839431761199</v>
       </c>
       <c r="D47">
-        <v>70.76623874646548</v>
+        <v>41.97339431761199</v>
       </c>
       <c r="E47">
-        <v>42.615</v>
+        <v>27.135</v>
       </c>
       <c r="F47">
-        <v>42.615</v>
+        <v>27.135</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -5024,45 +5024,45 @@
         <v>2.801</v>
       </c>
       <c r="M47">
-        <v>5.226901843236112</v>
+        <v>6.479838</v>
       </c>
       <c r="N47">
-        <v>-2.425901843236112</v>
+        <v>-3.678838</v>
       </c>
       <c r="O47">
-        <v>-0.7277705529708335</v>
+        <v>-1.1036514</v>
       </c>
       <c r="P47">
-        <v>-1.698131290265278</v>
+        <v>-2.575186599999999</v>
       </c>
       <c r="Q47">
-        <v>-1.299131290265278</v>
+        <v>-2.176186599999999</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1774822401835748</v>
+        <v>0.3018992602116284</v>
       </c>
       <c r="T47">
-        <v>1.719750143259839</v>
+        <v>1.707549417288273</v>
       </c>
       <c r="U47">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V47">
-        <v>0.1607644499939085</v>
+        <v>0.1296791679051236</v>
       </c>
       <c r="W47">
-        <v>0.1029356293144694</v>
+        <v>0.2078326147042565</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y47">
-        <v>0.535881499979695</v>
+        <v>0.4322638930170786</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5073,25 +5073,25 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.1450118056757312</v>
+        <v>0.2615692697333111</v>
       </c>
       <c r="C48">
-        <v>26.61836475951787</v>
+        <v>13.85856142348921</v>
       </c>
       <c r="D48">
-        <v>70.18036475951787</v>
+        <v>41.59656142348921</v>
       </c>
       <c r="E48">
-        <v>43.562</v>
+        <v>27.738</v>
       </c>
       <c r="F48">
-        <v>43.562</v>
+        <v>27.738</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -5106,45 +5106,45 @@
         <v>2.801</v>
       </c>
       <c r="M48">
-        <v>5.343055217530248</v>
+        <v>6.6238344</v>
       </c>
       <c r="N48">
-        <v>-2.542055217530248</v>
+        <v>-3.8228344</v>
       </c>
       <c r="O48">
-        <v>-0.7626165652590743</v>
+        <v>-1.14685032</v>
       </c>
       <c r="P48">
-        <v>-1.779438652271173</v>
+        <v>-2.67598408</v>
       </c>
       <c r="Q48">
-        <v>-1.380438652271173</v>
+        <v>-2.27698408</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1804893187054929</v>
+        <v>0.306771468734066</v>
       </c>
       <c r="T48">
-        <v>1.751597368135021</v>
+        <v>1.739170702793612</v>
       </c>
       <c r="U48">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V48">
-        <v>0.1572695706462148</v>
+        <v>0.12686005555936</v>
       </c>
       <c r="W48">
-        <v>0.103364290379924</v>
+        <v>0.2085058187324249</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5242319021540494</v>
+        <v>0.4228668518645333</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5155,25 +5155,25 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.146087346058985</v>
+        <v>0.2635692697333111</v>
       </c>
       <c r="C49">
-        <v>25.09511202456775</v>
+        <v>12.88543465773654</v>
       </c>
       <c r="D49">
-        <v>69.60411202456775</v>
+        <v>41.22643465773654</v>
       </c>
       <c r="E49">
-        <v>44.50900000000001</v>
+        <v>28.341</v>
       </c>
       <c r="F49">
-        <v>44.50900000000001</v>
+        <v>28.341</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -5188,45 +5188,45 @@
         <v>2.801</v>
       </c>
       <c r="M49">
-        <v>5.459208591824384</v>
+        <v>6.7678308</v>
       </c>
       <c r="N49">
-        <v>-2.658208591824384</v>
+        <v>-3.9668308</v>
       </c>
       <c r="O49">
-        <v>-0.7974625775473153</v>
+        <v>-1.19004924</v>
       </c>
       <c r="P49">
-        <v>-1.860746014277069</v>
+        <v>-2.77678156</v>
       </c>
       <c r="Q49">
-        <v>-1.461746014277069</v>
+        <v>-2.37778156</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1836098718886154</v>
+        <v>0.3118275341818786</v>
       </c>
       <c r="T49">
-        <v>1.784646375080965</v>
+        <v>1.771985244355756</v>
       </c>
       <c r="U49">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V49">
-        <v>0.1539234095686358</v>
+        <v>0.1241609054410758</v>
       </c>
       <c r="W49">
-        <v>0.1037747105489762</v>
+        <v>0.2091503757806711</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.5130780318954525</v>
+        <v>0.4138696848035858</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5237,25 +5237,25 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1471628864422388</v>
+        <v>0.2655692697333111</v>
       </c>
       <c r="C50">
-        <v>23.58124547076359</v>
+        <v>11.91883658550903</v>
       </c>
       <c r="D50">
-        <v>69.03724547076359</v>
+        <v>40.86283658550903</v>
       </c>
       <c r="E50">
-        <v>45.456</v>
+        <v>28.944</v>
       </c>
       <c r="F50">
-        <v>45.456</v>
+        <v>28.944</v>
       </c>
       <c r="G50">
         <v>0</v>
       </c>
       <c r="H50">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -5270,45 +5270,45 @@
         <v>2.801</v>
       </c>
       <c r="M50">
-        <v>5.575361966118519</v>
+        <v>6.9118272</v>
       </c>
       <c r="N50">
-        <v>-2.774361966118519</v>
+        <v>-4.1108272</v>
       </c>
       <c r="O50">
-        <v>-0.8323085898355558</v>
+        <v>-1.23324816</v>
       </c>
       <c r="P50">
-        <v>-1.942053376282963</v>
+        <v>-2.87757904</v>
       </c>
       <c r="Q50">
-        <v>-1.543053376282963</v>
+        <v>-2.47857904</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1868504463480118</v>
+        <v>0.3170780636853763</v>
       </c>
       <c r="T50">
-        <v>1.818966497678675</v>
+        <v>1.806061883670289</v>
       </c>
       <c r="U50">
-        <v>0.122654038325381</v>
+        <v>0.2388</v>
       </c>
       <c r="V50">
-        <v>0.1507166718692892</v>
+        <v>0.1215742199110533</v>
       </c>
       <c r="W50">
-        <v>0.1041680298776513</v>
+        <v>0.2097680762852405</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y50">
-        <v>0.5023889062309641</v>
+        <v>0.4052473997035111</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5319,25 +5319,25 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1673550994833016</v>
+        <v>0.2675692697333111</v>
       </c>
       <c r="C51">
-        <v>13.47846170362157</v>
+        <v>10.95859597681062</v>
       </c>
       <c r="D51">
-        <v>59.88146170362157</v>
+        <v>40.50559597681062</v>
       </c>
       <c r="E51">
-        <v>46.403</v>
+        <v>29.547</v>
       </c>
       <c r="F51">
-        <v>46.403</v>
+        <v>29.547</v>
       </c>
       <c r="G51">
         <v>0</v>
       </c>
       <c r="H51">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -5352,37 +5352,37 @@
         <v>2.801</v>
       </c>
       <c r="M51">
-        <v>7.352837031994305</v>
+        <v>7.0558236</v>
       </c>
       <c r="N51">
-        <v>-4.551837031994305</v>
+        <v>-4.2548236</v>
       </c>
       <c r="O51">
-        <v>-1.365551109598292</v>
+        <v>-1.27644708</v>
       </c>
       <c r="P51">
-        <v>-3.186285922396014</v>
+        <v>-2.97837652</v>
       </c>
       <c r="Q51">
-        <v>-2.787285922396014</v>
+        <v>-2.57937652</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1933037432775194</v>
+        <v>0.3225344963066581</v>
       </c>
       <c r="T51">
-        <v>1.887311769344299</v>
+        <v>1.841474861781471</v>
       </c>
       <c r="U51">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V51">
-        <v>0.1142824186560389</v>
+        <v>0.1190931133822563</v>
       </c>
       <c r="W51">
-        <v>0.1403473273709524</v>
+        <v>0.2103605645243172</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3809413955201298</v>
+        <v>0.3969770446075211</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5401,25 +5401,25 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1687886601867032</v>
+        <v>0.2695692697333111</v>
       </c>
       <c r="C52">
-        <v>11.97290578767907</v>
+        <v>10.00454753761748</v>
       </c>
       <c r="D52">
-        <v>59.32290578767907</v>
+        <v>40.15454753761747</v>
       </c>
       <c r="E52">
-        <v>47.35</v>
+        <v>30.15</v>
       </c>
       <c r="F52">
-        <v>47.35</v>
+        <v>30.15</v>
       </c>
       <c r="G52">
         <v>0</v>
       </c>
       <c r="H52">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -5434,37 +5434,37 @@
         <v>2.801</v>
       </c>
       <c r="M52">
-        <v>7.502894930606434</v>
+        <v>7.19982</v>
       </c>
       <c r="N52">
-        <v>-4.701894930606434</v>
+        <v>-4.39882</v>
       </c>
       <c r="O52">
-        <v>-1.41056847918193</v>
+        <v>-1.319646</v>
       </c>
       <c r="P52">
-        <v>-3.291326451424504</v>
+        <v>-3.079174</v>
       </c>
       <c r="Q52">
-        <v>-2.892326451424504</v>
+        <v>-2.680174</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1968678181430698</v>
+        <v>0.3282091862327913</v>
       </c>
       <c r="T52">
-        <v>1.925058004731185</v>
+        <v>1.878304359017101</v>
       </c>
       <c r="U52">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V52">
-        <v>0.1119967702829182</v>
+        <v>0.1167112511146112</v>
       </c>
       <c r="W52">
-        <v>0.1407095022303365</v>
+        <v>0.2109293532338309</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3733225676097273</v>
+        <v>0.3890375037153707</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5483,25 +5483,25 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1702222208901047</v>
+        <v>0.2715692697333111</v>
       </c>
       <c r="C53">
-        <v>10.47767365136212</v>
+        <v>9.056531654862653</v>
       </c>
       <c r="D53">
-        <v>58.77467365136213</v>
+        <v>39.80953165486265</v>
       </c>
       <c r="E53">
-        <v>48.297</v>
+        <v>30.753</v>
       </c>
       <c r="F53">
-        <v>48.297</v>
+        <v>30.753</v>
       </c>
       <c r="G53">
         <v>0</v>
       </c>
       <c r="H53">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -5516,37 +5516,37 @@
         <v>2.801</v>
       </c>
       <c r="M53">
-        <v>7.652952829218563</v>
+        <v>7.343816400000001</v>
       </c>
       <c r="N53">
-        <v>-4.851952829218563</v>
+        <v>-4.5428164</v>
       </c>
       <c r="O53">
-        <v>-1.455585848765569</v>
+        <v>-1.36284492</v>
       </c>
       <c r="P53">
-        <v>-3.396366980452994</v>
+        <v>-3.17997148</v>
       </c>
       <c r="Q53">
-        <v>-2.997366980452994</v>
+        <v>-2.78097148</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.200577365452112</v>
+        <v>0.3341154961559095</v>
       </c>
       <c r="T53">
-        <v>1.964344902786924</v>
+        <v>1.916637101037858</v>
       </c>
       <c r="U53">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V53">
-        <v>0.1098007551793315</v>
+        <v>0.1144227952104031</v>
       </c>
       <c r="W53">
-        <v>0.1410574741540585</v>
+        <v>0.2114758365037558</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3660025172644384</v>
+        <v>0.3814093173680104</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5565,25 +5565,25 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1716557815935063</v>
+        <v>0.2735692697333111</v>
       </c>
       <c r="C54">
-        <v>8.992481694193685</v>
+        <v>8.114394154455677</v>
       </c>
       <c r="D54">
-        <v>58.23648169419369</v>
+        <v>39.47039415445568</v>
       </c>
       <c r="E54">
-        <v>49.244</v>
+        <v>31.356</v>
       </c>
       <c r="F54">
-        <v>49.244</v>
+        <v>31.356</v>
       </c>
       <c r="G54">
         <v>0</v>
       </c>
       <c r="H54">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -5598,37 +5598,37 @@
         <v>2.801</v>
       </c>
       <c r="M54">
-        <v>7.80301072783069</v>
+        <v>7.487812799999999</v>
       </c>
       <c r="N54">
-        <v>-5.00201072783069</v>
+        <v>-4.686812799999999</v>
       </c>
       <c r="O54">
-        <v>-1.500603218349207</v>
+        <v>-1.40604384</v>
       </c>
       <c r="P54">
-        <v>-3.501407509481483</v>
+        <v>-3.28076896</v>
       </c>
       <c r="Q54">
-        <v>-3.102407509481483</v>
+        <v>-2.88176896</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.2044414772323644</v>
+        <v>0.3402679023258243</v>
       </c>
       <c r="T54">
-        <v>2.005268754928318</v>
+        <v>1.956567040642813</v>
       </c>
       <c r="U54">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V54">
-        <v>0.1076892021951136</v>
+        <v>0.1122223568409723</v>
       </c>
       <c r="W54">
-        <v>0.1413920625422527</v>
+        <v>0.2120013011863758</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3589640073170455</v>
+        <v>0.374074522803241</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5647,25 +5647,25 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1730893422969079</v>
+        <v>0.2755692697333111</v>
       </c>
       <c r="C55">
-        <v>7.517056609011263</v>
+        <v>7.177986071566249</v>
       </c>
       <c r="D55">
-        <v>57.70805660901127</v>
+        <v>39.13698607156625</v>
       </c>
       <c r="E55">
-        <v>50.191</v>
+        <v>31.959</v>
       </c>
       <c r="F55">
-        <v>50.191</v>
+        <v>31.959</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -5680,37 +5680,37 @@
         <v>2.801</v>
       </c>
       <c r="M55">
-        <v>7.95306862644282</v>
+        <v>7.6318092</v>
       </c>
       <c r="N55">
-        <v>-5.15206862644282</v>
+        <v>-4.8308092</v>
       </c>
       <c r="O55">
-        <v>-1.545620587932846</v>
+        <v>-1.44924276</v>
       </c>
       <c r="P55">
-        <v>-3.606448038509974</v>
+        <v>-3.38156644</v>
       </c>
       <c r="Q55">
-        <v>-3.207448038509974</v>
+        <v>-2.98256644</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.2084700193011381</v>
+        <v>0.3466821130136077</v>
       </c>
       <c r="T55">
-        <v>2.047934047586367</v>
+        <v>1.998196126613937</v>
       </c>
       <c r="U55">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V55">
-        <v>0.1056573304555832</v>
+        <v>0.1101049538817087</v>
       </c>
       <c r="W55">
-        <v>0.1417140249535339</v>
+        <v>0.212506937013048</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5718,7 +5718,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3521911015186105</v>
+        <v>0.3670165129390289</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5729,25 +5729,25 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1745229030003094</v>
+        <v>0.2775692697333111</v>
       </c>
       <c r="C56">
-        <v>6.051134919169805</v>
+        <v>6.247163432452943</v>
       </c>
       <c r="D56">
-        <v>57.18913491916981</v>
+        <v>38.80916343245294</v>
       </c>
       <c r="E56">
-        <v>51.13800000000001</v>
+        <v>32.562</v>
       </c>
       <c r="F56">
-        <v>51.13800000000001</v>
+        <v>32.562</v>
       </c>
       <c r="G56">
         <v>0</v>
       </c>
       <c r="H56">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -5762,37 +5762,37 @@
         <v>2.801</v>
       </c>
       <c r="M56">
-        <v>8.103126525054948</v>
+        <v>7.7758056</v>
       </c>
       <c r="N56">
-        <v>-5.302126525054948</v>
+        <v>-4.9748056</v>
       </c>
       <c r="O56">
-        <v>-1.590637957516484</v>
+        <v>-1.49244168</v>
       </c>
       <c r="P56">
-        <v>-3.711488567538464</v>
+        <v>-3.48236392</v>
       </c>
       <c r="Q56">
-        <v>-3.312488567538464</v>
+        <v>-3.08336392</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.212673715372902</v>
+        <v>0.3533752024269471</v>
       </c>
       <c r="T56">
-        <v>2.09245435296868</v>
+        <v>2.041635172844675</v>
       </c>
       <c r="U56">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V56">
-        <v>0.1037007132249242</v>
+        <v>0.1080659732542696</v>
       </c>
       <c r="W56">
-        <v>0.1420240628310639</v>
+        <v>0.2129938455868804</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3456690440830807</v>
+        <v>0.3602199108475654</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5811,25 +5811,25 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.175956463703711</v>
+        <v>0.2795692697333111</v>
       </c>
       <c r="C57">
-        <v>4.594462540491477</v>
+        <v>5.321787047165564</v>
       </c>
       <c r="D57">
-        <v>56.67946254049149</v>
+        <v>38.48678704716556</v>
       </c>
       <c r="E57">
-        <v>52.08500000000001</v>
+        <v>33.165</v>
       </c>
       <c r="F57">
-        <v>52.08500000000001</v>
+        <v>33.165</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -5844,37 +5844,37 @@
         <v>2.801</v>
       </c>
       <c r="M57">
-        <v>8.253184423667077</v>
+        <v>7.919802</v>
       </c>
       <c r="N57">
-        <v>-5.452184423667077</v>
+        <v>-5.118802</v>
       </c>
       <c r="O57">
-        <v>-1.635655327100123</v>
+        <v>-1.5356406</v>
       </c>
       <c r="P57">
-        <v>-3.816529096566954</v>
+        <v>-3.5831614</v>
       </c>
       <c r="Q57">
-        <v>-3.417529096566954</v>
+        <v>-3.1841614</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.2170642423811887</v>
+        <v>0.3603657624808793</v>
       </c>
       <c r="T57">
-        <v>2.138953338590206</v>
+        <v>2.087004843352334</v>
       </c>
       <c r="U57">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V57">
-        <v>0.1018152457117438</v>
+        <v>0.1061011373769193</v>
       </c>
       <c r="W57">
-        <v>0.1423228266039565</v>
+        <v>0.2134630483943917</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3393841523724793</v>
+        <v>0.3536704579230643</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5893,25 +5893,25 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1773900244071126</v>
+        <v>0.2815692697333111</v>
       </c>
       <c r="C58">
-        <v>3.146794366432047</v>
+        <v>4.401722312494293</v>
       </c>
       <c r="D58">
-        <v>56.17879436643205</v>
+        <v>38.16972231249429</v>
       </c>
       <c r="E58">
-        <v>53.032</v>
+        <v>33.768</v>
       </c>
       <c r="F58">
-        <v>53.032</v>
+        <v>33.768</v>
       </c>
       <c r="G58">
         <v>0</v>
       </c>
       <c r="H58">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -5926,37 +5926,37 @@
         <v>2.801</v>
       </c>
       <c r="M58">
-        <v>8.403242322279207</v>
+        <v>8.063798400000001</v>
       </c>
       <c r="N58">
-        <v>-5.602242322279206</v>
+        <v>-5.262798400000001</v>
       </c>
       <c r="O58">
-        <v>-1.680672696683762</v>
+        <v>-1.57883952</v>
       </c>
       <c r="P58">
-        <v>-3.921569625595445</v>
+        <v>-3.68395888</v>
       </c>
       <c r="Q58">
-        <v>-3.522569625595445</v>
+        <v>-3.28495888</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.221654338798943</v>
+        <v>0.3676740752645355</v>
       </c>
       <c r="T58">
-        <v>2.187565914467256</v>
+        <v>2.134436771610342</v>
       </c>
       <c r="U58">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V58">
-        <v>0.09999711632403407</v>
+        <v>0.1042064742094743</v>
       </c>
       <c r="W58">
-        <v>0.142610920242103</v>
+        <v>0.2139154939587776</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3333237210801135</v>
+        <v>0.3473549140315809</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -5975,25 +5975,25 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1788235851105142</v>
+        <v>0.2835692697333111</v>
       </c>
       <c r="C59">
-        <v>1.707893875040817</v>
+        <v>3.486839024579247</v>
       </c>
       <c r="D59">
-        <v>55.68689387504082</v>
+        <v>37.85783902457925</v>
       </c>
       <c r="E59">
-        <v>53.97900000000001</v>
+        <v>34.371</v>
       </c>
       <c r="F59">
-        <v>53.97900000000001</v>
+        <v>34.371</v>
       </c>
       <c r="G59">
         <v>0</v>
       </c>
       <c r="H59">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -6008,37 +6008,37 @@
         <v>2.801</v>
       </c>
       <c r="M59">
-        <v>8.553300220891336</v>
+        <v>8.2077948</v>
       </c>
       <c r="N59">
-        <v>-5.752300220891335</v>
+        <v>-5.4067948</v>
       </c>
       <c r="O59">
-        <v>-1.725690066267401</v>
+        <v>-1.62203844</v>
       </c>
       <c r="P59">
-        <v>-4.026610154623935</v>
+        <v>-3.78475636</v>
       </c>
       <c r="Q59">
-        <v>-3.627610154623935</v>
+        <v>-3.38575636</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.226457928073337</v>
+        <v>0.3753223095730132</v>
       </c>
       <c r="T59">
-        <v>2.238439540385099</v>
+        <v>2.184074836066396</v>
       </c>
       <c r="U59">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V59">
-        <v>0.09824278094992821</v>
+        <v>0.1023782904514133</v>
       </c>
       <c r="W59">
-        <v>0.1428889053315425</v>
+        <v>0.2143520642402025</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6046,7 +6046,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3274759364997607</v>
+        <v>0.3412609681713777</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6057,25 +6057,25 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1802571458139157</v>
+        <v>0.2855692697333111</v>
       </c>
       <c r="C60">
-        <v>0.2775327563902437</v>
+        <v>2.577011200632668</v>
       </c>
       <c r="D60">
-        <v>55.20353275639024</v>
+        <v>37.55101120063267</v>
       </c>
       <c r="E60">
-        <v>54.92599999999999</v>
+        <v>34.974</v>
       </c>
       <c r="F60">
-        <v>54.92599999999999</v>
+        <v>34.974</v>
       </c>
       <c r="G60">
         <v>0</v>
       </c>
       <c r="H60">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -6090,37 +6090,37 @@
         <v>2.801</v>
       </c>
       <c r="M60">
-        <v>8.703358119503463</v>
+        <v>8.351791199999999</v>
       </c>
       <c r="N60">
-        <v>-5.902358119503463</v>
+        <v>-5.550791199999999</v>
       </c>
       <c r="O60">
-        <v>-1.770707435851039</v>
+        <v>-1.66523736</v>
       </c>
       <c r="P60">
-        <v>-4.131650683652424</v>
+        <v>-3.885553839999999</v>
       </c>
       <c r="Q60">
-        <v>-3.732650683652424</v>
+        <v>-3.486553839999999</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.2314902596941307</v>
+        <v>0.3833347455152277</v>
       </c>
       <c r="T60">
-        <v>2.291735719918077</v>
+        <v>2.236076617877501</v>
       </c>
       <c r="U60">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V60">
-        <v>0.09654893989906739</v>
+        <v>0.1006131475125959</v>
       </c>
       <c r="W60">
-        <v>0.1431573047282428</v>
+        <v>0.2147735803739921</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.321829799663558</v>
+        <v>0.3353771583753196</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6139,25 +6139,25 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1816907065173173</v>
+        <v>0.2875692697333111</v>
       </c>
       <c r="C61">
-        <v>-1.144509440758213</v>
+        <v>1.67211690926068</v>
       </c>
       <c r="D61">
-        <v>54.72849055924178</v>
+        <v>37.24911690926068</v>
       </c>
       <c r="E61">
-        <v>55.873</v>
+        <v>35.577</v>
       </c>
       <c r="F61">
-        <v>55.873</v>
+        <v>35.577</v>
       </c>
       <c r="G61">
         <v>0</v>
       </c>
       <c r="H61">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -6172,37 +6172,37 @@
         <v>2.801</v>
       </c>
       <c r="M61">
-        <v>8.853416018115592</v>
+        <v>8.4957876</v>
       </c>
       <c r="N61">
-        <v>-6.052416018115592</v>
+        <v>-5.6947876</v>
       </c>
       <c r="O61">
-        <v>-1.815724805434678</v>
+        <v>-1.70843628</v>
       </c>
       <c r="P61">
-        <v>-4.236691212680914</v>
+        <v>-3.98635132</v>
       </c>
       <c r="Q61">
-        <v>-3.837691212680914</v>
+        <v>-3.58735132</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.2367680709061827</v>
+        <v>0.3917380319912089</v>
       </c>
       <c r="T61">
-        <v>2.347631713086811</v>
+        <v>2.290615071972074</v>
       </c>
       <c r="U61">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V61">
-        <v>0.09491251718891369</v>
+        <v>0.09890783992763663</v>
       </c>
       <c r="W61">
-        <v>0.1434166058403091</v>
+        <v>0.2151808078252804</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.316375057296379</v>
+        <v>0.3296927997587887</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6221,25 +6221,25 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1831242672207189</v>
+        <v>0.289569269733311</v>
       </c>
       <c r="C62">
-        <v>-2.558445644200518</v>
+        <v>0.7720381089046953</v>
       </c>
       <c r="D62">
-        <v>54.26155435579948</v>
+        <v>36.95203810890469</v>
       </c>
       <c r="E62">
-        <v>56.82</v>
+        <v>36.18</v>
       </c>
       <c r="F62">
-        <v>56.82</v>
+        <v>36.18</v>
       </c>
       <c r="G62">
         <v>0</v>
       </c>
       <c r="H62">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -6254,37 +6254,37 @@
         <v>2.801</v>
       </c>
       <c r="M62">
-        <v>9.003473916727721</v>
+        <v>8.639784000000001</v>
       </c>
       <c r="N62">
-        <v>-6.202473916727721</v>
+        <v>-5.838784</v>
       </c>
       <c r="O62">
-        <v>-1.860742175018316</v>
+        <v>-1.7516352</v>
       </c>
       <c r="P62">
-        <v>-4.341731741709404</v>
+        <v>-4.0871488</v>
       </c>
       <c r="Q62">
-        <v>-3.942731741709404</v>
+        <v>-3.6881488</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2423097726788373</v>
+        <v>0.4005614827909891</v>
       </c>
       <c r="T62">
-        <v>2.406322505913981</v>
+        <v>2.347880448771376</v>
       </c>
       <c r="U62">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V62">
-        <v>0.0933306419024318</v>
+        <v>0.09725937592884268</v>
       </c>
       <c r="W62">
-        <v>0.1436672635819733</v>
+        <v>0.2155744610281924</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3111021396747727</v>
+        <v>0.3241979197628089</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6303,25 +6303,25 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1845578279241205</v>
+        <v>0.2915692697333111</v>
       </c>
       <c r="C63">
-        <v>-3.964481576519866</v>
+        <v>-0.1233395060474152</v>
       </c>
       <c r="D63">
-        <v>53.80251842348014</v>
+        <v>36.65966049395258</v>
       </c>
       <c r="E63">
-        <v>57.767</v>
+        <v>36.78299999999999</v>
       </c>
       <c r="F63">
-        <v>57.767</v>
+        <v>36.78299999999999</v>
       </c>
       <c r="G63">
         <v>0</v>
       </c>
       <c r="H63">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -6336,37 +6336,37 @@
         <v>2.801</v>
       </c>
       <c r="M63">
-        <v>9.15353181533985</v>
+        <v>8.783780399999999</v>
       </c>
       <c r="N63">
-        <v>-6.35253181533985</v>
+        <v>-5.982780399999999</v>
       </c>
       <c r="O63">
-        <v>-1.905759544601955</v>
+        <v>-1.79483412</v>
       </c>
       <c r="P63">
-        <v>-4.446772270737895</v>
+        <v>-4.187946279999999</v>
       </c>
       <c r="Q63">
-        <v>-4.047772270737895</v>
+        <v>-3.788946279999999</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.248135664285987</v>
+        <v>0.4098374182471683</v>
       </c>
       <c r="T63">
-        <v>2.468023082988699</v>
+        <v>2.408082511560385</v>
       </c>
       <c r="U63">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V63">
-        <v>0.09180063137944111</v>
+        <v>0.09566495993000922</v>
       </c>
       <c r="W63">
-        <v>0.1439097030370255</v>
+        <v>0.2159552075687138</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.306002104598137</v>
+        <v>0.3188831997666973</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6385,25 +6385,25 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.185991388627522</v>
+        <v>0.2935692697333111</v>
       </c>
       <c r="C64">
-        <v>-5.362816057299661</v>
+        <v>-1.014126651901599</v>
       </c>
       <c r="D64">
-        <v>53.35118394270034</v>
+        <v>36.3718733480984</v>
       </c>
       <c r="E64">
-        <v>58.714</v>
+        <v>37.386</v>
       </c>
       <c r="F64">
-        <v>58.714</v>
+        <v>37.386</v>
       </c>
       <c r="G64">
         <v>0</v>
       </c>
       <c r="H64">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -6418,37 +6418,37 @@
         <v>2.801</v>
       </c>
       <c r="M64">
-        <v>9.303589713951977</v>
+        <v>8.9277768</v>
       </c>
       <c r="N64">
-        <v>-6.502589713951977</v>
+        <v>-6.1267768</v>
       </c>
       <c r="O64">
-        <v>-1.950776914185593</v>
+        <v>-1.83803304</v>
       </c>
       <c r="P64">
-        <v>-4.551812799766384</v>
+        <v>-4.28874376</v>
       </c>
       <c r="Q64">
-        <v>-4.152812799766384</v>
+        <v>-3.88974376</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2542681817671971</v>
+        <v>0.4196015608326201</v>
       </c>
       <c r="T64">
-        <v>2.532971058856822</v>
+        <v>2.47145310396987</v>
       </c>
       <c r="U64">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V64">
-        <v>0.09031997603461143</v>
+        <v>0.09412197670533162</v>
       </c>
       <c r="W64">
-        <v>0.1441443218644953</v>
+        <v>0.2163236719627668</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3010665867820381</v>
+        <v>0.3137399223511054</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6467,25 +6467,25 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1874249493309236</v>
+        <v>0.2955692697333111</v>
       </c>
       <c r="C65">
-        <v>-6.753641290251458</v>
+        <v>-1.900430595444966</v>
       </c>
       <c r="D65">
-        <v>52.90735870974854</v>
+        <v>36.08856940455503</v>
       </c>
       <c r="E65">
-        <v>59.661</v>
+        <v>37.989</v>
       </c>
       <c r="F65">
-        <v>59.661</v>
+        <v>37.989</v>
       </c>
       <c r="G65">
         <v>0</v>
       </c>
       <c r="H65">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -6500,37 +6500,37 @@
         <v>2.801</v>
       </c>
       <c r="M65">
-        <v>9.453647612564106</v>
+        <v>9.071773199999999</v>
       </c>
       <c r="N65">
-        <v>-6.652647612564106</v>
+        <v>-6.270773199999999</v>
       </c>
       <c r="O65">
-        <v>-1.995794283769232</v>
+        <v>-1.88123196</v>
       </c>
       <c r="P65">
-        <v>-4.656853328794874</v>
+        <v>-4.389541239999999</v>
       </c>
       <c r="Q65">
-        <v>-4.257853328794874</v>
+        <v>-3.990541239999999</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2607321866798241</v>
+        <v>0.4298934949091774</v>
       </c>
       <c r="T65">
-        <v>2.601429736123223</v>
+        <v>2.538249133806893</v>
       </c>
       <c r="U65">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V65">
-        <v>0.08888632562136363</v>
+        <v>0.09262797707508828</v>
       </c>
       <c r="W65">
-        <v>0.1443714924752201</v>
+        <v>0.2166804390744689</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2962877520712121</v>
+        <v>0.3087599235836276</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6549,25 +6549,25 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.1888585100343251</v>
+        <v>0.2975692697333111</v>
       </c>
       <c r="C66">
-        <v>-8.137143136129872</v>
+        <v>-2.782355287250518</v>
       </c>
       <c r="D66">
-        <v>52.47085686387013</v>
+        <v>35.80964471274948</v>
       </c>
       <c r="E66">
-        <v>60.608</v>
+        <v>38.592</v>
       </c>
       <c r="F66">
-        <v>60.608</v>
+        <v>38.592</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -6582,37 +6582,37 @@
         <v>2.801</v>
       </c>
       <c r="M66">
-        <v>9.603705511176235</v>
+        <v>9.2157696</v>
       </c>
       <c r="N66">
-        <v>-6.802705511176235</v>
+        <v>-6.4147696</v>
       </c>
       <c r="O66">
-        <v>-2.040811653352871</v>
+        <v>-1.92443088</v>
       </c>
       <c r="P66">
-        <v>-4.761893857823365</v>
+        <v>-4.49033872</v>
       </c>
       <c r="Q66">
-        <v>-4.362893857823365</v>
+        <v>-4.09133872</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2675553029764859</v>
+        <v>0.4407572031010991</v>
       </c>
       <c r="T66">
-        <v>2.673691673237757</v>
+        <v>2.608756054190418</v>
       </c>
       <c r="U66">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V66">
-        <v>0.08749747678352983</v>
+        <v>0.09118066493329002</v>
       </c>
       <c r="W66">
-        <v>0.1445915640043597</v>
+        <v>0.2170260572139303</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6620,7 +6620,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2916582559450994</v>
+        <v>0.3039355497776334</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6631,25 +6631,25 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1902920707377267</v>
+        <v>0.2995692697333111</v>
       </c>
       <c r="C67">
-        <v>-9.513501372248115</v>
+        <v>-3.660001488847598</v>
       </c>
       <c r="D67">
-        <v>52.04149862775189</v>
+        <v>35.5349985111524</v>
       </c>
       <c r="E67">
-        <v>61.55500000000001</v>
+        <v>39.195</v>
       </c>
       <c r="F67">
-        <v>61.55500000000001</v>
+        <v>39.195</v>
       </c>
       <c r="G67">
         <v>0</v>
       </c>
       <c r="H67">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -6664,37 +6664,37 @@
         <v>2.801</v>
       </c>
       <c r="M67">
-        <v>9.753763409788364</v>
+        <v>9.359766</v>
       </c>
       <c r="N67">
-        <v>-6.952763409788364</v>
+        <v>-6.558766</v>
       </c>
       <c r="O67">
-        <v>-2.085829022936509</v>
+        <v>-1.9676298</v>
       </c>
       <c r="P67">
-        <v>-4.866934386851855</v>
+        <v>-4.5911362</v>
       </c>
       <c r="Q67">
-        <v>-4.467934386851855</v>
+        <v>-4.1921362</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2747683116329569</v>
+        <v>0.4522416946182733</v>
       </c>
       <c r="T67">
-        <v>2.750082863901693</v>
+        <v>2.683291941453001</v>
       </c>
       <c r="U67">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V67">
-        <v>0.08615136175609089</v>
+        <v>0.08977788547277786</v>
       </c>
       <c r="W67">
-        <v>0.1448048641018335</v>
+        <v>0.2173610409491007</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2871712058536363</v>
+        <v>0.2992596182425928</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6713,25 +6713,25 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1917256314411283</v>
+        <v>0.3015692697333111</v>
       </c>
       <c r="C68">
-        <v>-10.88288993935559</v>
+        <v>-4.53346689408481</v>
       </c>
       <c r="D68">
-        <v>51.61911006064441</v>
+        <v>35.26453310591519</v>
       </c>
       <c r="E68">
-        <v>62.502</v>
+        <v>39.798</v>
       </c>
       <c r="F68">
-        <v>62.502</v>
+        <v>39.798</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -6746,37 +6746,37 @@
         <v>2.801</v>
       </c>
       <c r="M68">
-        <v>9.903821308400493</v>
+        <v>9.503762400000001</v>
       </c>
       <c r="N68">
-        <v>-7.102821308400493</v>
+        <v>-6.702762400000001</v>
       </c>
       <c r="O68">
-        <v>-2.130846392520148</v>
+        <v>-2.010828720000001</v>
       </c>
       <c r="P68">
-        <v>-4.971974915880345</v>
+        <v>-4.69193368</v>
       </c>
       <c r="Q68">
-        <v>-4.572974915880345</v>
+        <v>-4.29293368</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2824056149162791</v>
+        <v>0.4644017444599873</v>
       </c>
       <c r="T68">
-        <v>2.830967654016449</v>
+        <v>2.762212292672208</v>
       </c>
       <c r="U68">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V68">
-        <v>0.08484603809311982</v>
+        <v>0.08841761448076607</v>
       </c>
       <c r="W68">
-        <v>0.14501170055999</v>
+        <v>0.2176858736619931</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.282820126977066</v>
+        <v>0.2947253816025535</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6795,25 +6795,25 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1931591921445299</v>
+        <v>0.3035692697333111</v>
       </c>
       <c r="C69">
-        <v>-12.24547717658982</v>
+        <v>-5.402846244992375</v>
       </c>
       <c r="D69">
-        <v>51.20352282341019</v>
+        <v>34.99815375500763</v>
       </c>
       <c r="E69">
-        <v>63.44900000000001</v>
+        <v>40.401</v>
       </c>
       <c r="F69">
-        <v>63.44900000000001</v>
+        <v>40.401</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -6828,37 +6828,37 @@
         <v>2.801</v>
       </c>
       <c r="M69">
-        <v>10.05387920701262</v>
+        <v>9.647758800000002</v>
       </c>
       <c r="N69">
-        <v>-7.252879207012622</v>
+        <v>-6.846758800000002</v>
       </c>
       <c r="O69">
-        <v>-2.175863762103786</v>
+        <v>-2.054027640000001</v>
       </c>
       <c r="P69">
-        <v>-5.077015444908836</v>
+        <v>-4.792731160000001</v>
       </c>
       <c r="Q69">
-        <v>-4.678015444908836</v>
+        <v>-4.393731160000001</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2905057850652574</v>
+        <v>0.4772987670193807</v>
       </c>
       <c r="T69">
-        <v>2.916754552623008</v>
+        <v>2.845915695480456</v>
       </c>
       <c r="U69">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V69">
-        <v>0.08357967931561056</v>
+        <v>0.08709794859299343</v>
       </c>
       <c r="W69">
-        <v>0.1452123627955149</v>
+        <v>0.2180010098759932</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2785989310520353</v>
+        <v>0.2903264953099781</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6877,25 +6877,25 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.1945927528479314</v>
+        <v>0.3055692697333111</v>
       </c>
       <c r="C70">
-        <v>-13.60142604516922</v>
+        <v>-6.268231442432807</v>
       </c>
       <c r="D70">
-        <v>50.79457395483078</v>
+        <v>34.73576855756719</v>
       </c>
       <c r="E70">
-        <v>64.396</v>
+        <v>41.004</v>
       </c>
       <c r="F70">
-        <v>64.396</v>
+        <v>41.004</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -6910,37 +6910,37 @@
         <v>2.801</v>
       </c>
       <c r="M70">
-        <v>10.20393710562475</v>
+        <v>9.791755200000001</v>
       </c>
       <c r="N70">
-        <v>-7.402937105624749</v>
+        <v>-6.990755200000001</v>
       </c>
       <c r="O70">
-        <v>-2.220881131687425</v>
+        <v>-2.097226560000001</v>
       </c>
       <c r="P70">
-        <v>-5.182055973937325</v>
+        <v>-4.89352864</v>
       </c>
       <c r="Q70">
-        <v>-4.783055973937325</v>
+        <v>-4.49452864</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2991122158485466</v>
+        <v>0.4910018534887365</v>
       </c>
       <c r="T70">
-        <v>3.007903132392477</v>
+        <v>2.93485056096422</v>
       </c>
       <c r="U70">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V70">
-        <v>0.08235056638449866</v>
+        <v>0.08581709640780236</v>
       </c>
       <c r="W70">
-        <v>0.1454071232005831</v>
+        <v>0.2183068773778168</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2745018879483289</v>
+        <v>0.2860569880260079</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -6959,25 +6959,25 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.196026313551333</v>
+        <v>0.3075692697333111</v>
       </c>
       <c r="C71">
-        <v>-14.95089434145168</v>
+        <v>-7.129711651811164</v>
       </c>
       <c r="D71">
-        <v>50.39210565854832</v>
+        <v>34.47728834818884</v>
       </c>
       <c r="E71">
-        <v>65.343</v>
+        <v>41.607</v>
       </c>
       <c r="F71">
-        <v>65.343</v>
+        <v>41.607</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -6992,37 +6992,37 @@
         <v>2.801</v>
       </c>
       <c r="M71">
-        <v>10.35399500423688</v>
+        <v>9.9357516</v>
       </c>
       <c r="N71">
-        <v>-7.552995004236879</v>
+        <v>-7.1347516</v>
       </c>
       <c r="O71">
-        <v>-2.265898501271063</v>
+        <v>-2.14042548</v>
       </c>
       <c r="P71">
-        <v>-5.287096502965815</v>
+        <v>-4.994326119999999</v>
       </c>
       <c r="Q71">
-        <v>-4.888096502965815</v>
+        <v>-4.595326119999999</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.3082739002307578</v>
+        <v>0.5055890100528893</v>
       </c>
       <c r="T71">
-        <v>3.104932265695461</v>
+        <v>3.029523159705002</v>
       </c>
       <c r="U71">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V71">
-        <v>0.0811570799151581</v>
+        <v>0.08457337037290669</v>
       </c>
       <c r="W71">
-        <v>0.145596238376519</v>
+        <v>0.2186038791549499</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2705235997171936</v>
+        <v>0.2819112345763556</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7041,25 +7041,25 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1974598742547345</v>
+        <v>0.3095692697333111</v>
       </c>
       <c r="C72">
-        <v>-16.29403489994341</v>
+        <v>-7.987373404100452</v>
       </c>
       <c r="D72">
-        <v>49.99596510005659</v>
+        <v>34.22262659589955</v>
       </c>
       <c r="E72">
-        <v>66.29000000000001</v>
+        <v>42.21</v>
       </c>
       <c r="F72">
-        <v>66.29000000000001</v>
+        <v>42.21</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -7074,37 +7074,37 @@
         <v>2.801</v>
       </c>
       <c r="M72">
-        <v>10.50405290284901</v>
+        <v>10.079748</v>
       </c>
       <c r="N72">
-        <v>-7.703052902849008</v>
+        <v>-7.278748</v>
       </c>
       <c r="O72">
-        <v>-2.310915870854702</v>
+        <v>-2.1836244</v>
       </c>
       <c r="P72">
-        <v>-5.392137031994306</v>
+        <v>-5.0951236</v>
       </c>
       <c r="Q72">
-        <v>-4.993137031994306</v>
+        <v>-4.6961236</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.3180463635717831</v>
+        <v>0.5211486437213189</v>
       </c>
       <c r="T72">
-        <v>3.208430007885309</v>
+        <v>3.130507265028502</v>
       </c>
       <c r="U72">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V72">
-        <v>0.07999769305922727</v>
+        <v>0.08336517936757945</v>
       </c>
       <c r="W72">
-        <v>0.1457799502617138</v>
+        <v>0.218892395167022</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2666589768640909</v>
+        <v>0.2778839312252648</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7123,25 +7123,25 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1988934349581361</v>
+        <v>0.3115692697333111</v>
       </c>
       <c r="C73">
-        <v>-17.63099578680752</v>
+        <v>-8.841300692422621</v>
       </c>
       <c r="D73">
-        <v>49.60600421319247</v>
+        <v>33.97169930757737</v>
       </c>
       <c r="E73">
-        <v>67.23699999999999</v>
+        <v>42.813</v>
       </c>
       <c r="F73">
-        <v>67.23699999999999</v>
+        <v>42.813</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -7156,37 +7156,37 @@
         <v>2.801</v>
       </c>
       <c r="M73">
-        <v>10.65411080146113</v>
+        <v>10.2237444</v>
       </c>
       <c r="N73">
-        <v>-7.853110801461135</v>
+        <v>-7.422744399999999</v>
       </c>
       <c r="O73">
-        <v>-2.35593324043834</v>
+        <v>-2.22682332</v>
       </c>
       <c r="P73">
-        <v>-5.497177561022795</v>
+        <v>-5.195921079999999</v>
       </c>
       <c r="Q73">
-        <v>-5.098177561022795</v>
+        <v>-4.796921079999999</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.3284927899018445</v>
+        <v>0.537781355573778</v>
       </c>
       <c r="T73">
-        <v>3.319065525398595</v>
+        <v>3.238455791408795</v>
       </c>
       <c r="U73">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V73">
-        <v>0.07887096498797055</v>
+        <v>0.08219102191169805</v>
       </c>
       <c r="W73">
-        <v>0.1459584871642271</v>
+        <v>0.2191727839674865</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7194,7 +7194,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2629032166265685</v>
+        <v>0.2739700730389935</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7205,25 +7205,25 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2003269956615377</v>
+        <v>0.3135692697333111</v>
       </c>
       <c r="C74">
-        <v>-18.96192048438643</v>
+        <v>-9.691575064411523</v>
       </c>
       <c r="D74">
-        <v>49.22207951561357</v>
+        <v>33.72442493558847</v>
       </c>
       <c r="E74">
-        <v>68.184</v>
+        <v>43.416</v>
       </c>
       <c r="F74">
-        <v>68.184</v>
+        <v>43.416</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I74">
         <v>0</v>
@@ -7238,37 +7238,37 @@
         <v>2.801</v>
       </c>
       <c r="M74">
-        <v>10.80416870007326</v>
+        <v>10.3677408</v>
       </c>
       <c r="N74">
-        <v>-8.003168700073264</v>
+        <v>-7.5667408</v>
       </c>
       <c r="O74">
-        <v>-2.400950610021979</v>
+        <v>-2.27002224</v>
       </c>
       <c r="P74">
-        <v>-5.602218090051284</v>
+        <v>-5.29671856</v>
       </c>
       <c r="Q74">
-        <v>-5.203218090051284</v>
+        <v>-4.897718559999999</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.3396853895411961</v>
+        <v>0.5556021182728414</v>
       </c>
       <c r="T74">
-        <v>3.437603579877116</v>
+        <v>3.354114926816251</v>
       </c>
       <c r="U74">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V74">
-        <v>0.07777553491869318</v>
+        <v>0.08104947994070223</v>
       </c>
       <c r="W74">
-        <v>0.1461320647083372</v>
+        <v>0.2194453841901603</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2592517830623106</v>
+        <v>0.2701649331356741</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7287,25 +7287,25 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2017605563649393</v>
+        <v>0.3155692697333111</v>
       </c>
       <c r="C75">
-        <v>-20.28694806722152</v>
+        <v>-10.53827571057132</v>
       </c>
       <c r="D75">
-        <v>48.84405193277848</v>
+        <v>33.48072428942868</v>
       </c>
       <c r="E75">
-        <v>69.131</v>
+        <v>44.019</v>
       </c>
       <c r="F75">
-        <v>69.131</v>
+        <v>44.019</v>
       </c>
       <c r="G75">
         <v>0</v>
       </c>
       <c r="H75">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I75">
         <v>0</v>
@@ -7320,37 +7320,37 @@
         <v>2.801</v>
       </c>
       <c r="M75">
-        <v>10.95422659868539</v>
+        <v>10.5117372</v>
       </c>
       <c r="N75">
-        <v>-8.153226598685393</v>
+        <v>-7.710737200000001</v>
       </c>
       <c r="O75">
-        <v>-2.445967979605618</v>
+        <v>-2.31322116</v>
       </c>
       <c r="P75">
-        <v>-5.707258619079775</v>
+        <v>-5.39751604</v>
       </c>
       <c r="Q75">
-        <v>-5.308258619079775</v>
+        <v>-4.99851604</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.3517070706353144</v>
+        <v>0.5747429374681321</v>
       </c>
       <c r="T75">
-        <v>3.564922230983675</v>
+        <v>3.478341405587224</v>
       </c>
       <c r="U75">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V75">
-        <v>0.07671011663213574</v>
+        <v>0.07993921309219947</v>
       </c>
       <c r="W75">
-        <v>0.1463008867032936</v>
+        <v>0.2197105159135828</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2557003887737858</v>
+        <v>0.2664640436406648</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7369,25 +7369,25 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2031941170683408</v>
+        <v>0.317569269733311</v>
       </c>
       <c r="C76">
-        <v>-21.60621337002362</v>
+        <v>-11.38147954883122</v>
       </c>
       <c r="D76">
-        <v>48.47178662997639</v>
+        <v>33.24052045116878</v>
       </c>
       <c r="E76">
-        <v>70.078</v>
+        <v>44.622</v>
       </c>
       <c r="F76">
-        <v>70.078</v>
+        <v>44.622</v>
       </c>
       <c r="G76">
         <v>0</v>
       </c>
       <c r="H76">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I76">
         <v>0</v>
@@ -7402,37 +7402,37 @@
         <v>2.801</v>
       </c>
       <c r="M76">
-        <v>11.10428449729752</v>
+        <v>10.6557336</v>
       </c>
       <c r="N76">
-        <v>-8.303284497297522</v>
+        <v>-7.854733600000001</v>
       </c>
       <c r="O76">
-        <v>-2.490985349189256</v>
+        <v>-2.356420080000001</v>
       </c>
       <c r="P76">
-        <v>-5.812299148108266</v>
+        <v>-5.49831352</v>
       </c>
       <c r="Q76">
-        <v>-5.413299148108266</v>
+        <v>-5.09931352</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.3646534964289804</v>
+        <v>0.5953561273707524</v>
       </c>
       <c r="T76">
-        <v>3.702034624483048</v>
+        <v>3.612123767340578</v>
       </c>
       <c r="U76">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V76">
-        <v>0.07567349343440416</v>
+        <v>0.07885895345581839</v>
       </c>
       <c r="W76">
-        <v>0.1464651459416297</v>
+        <v>0.2199684819147506</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2522449781146806</v>
+        <v>0.2628631781860612</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7451,25 +7451,25 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2046276777717424</v>
+        <v>0.3195692697333111</v>
       </c>
       <c r="C77">
-        <v>-22.91984714802035</v>
+        <v>-12.22126130548673</v>
       </c>
       <c r="D77">
-        <v>48.10515285197966</v>
+        <v>33.00373869451327</v>
       </c>
       <c r="E77">
-        <v>71.02500000000001</v>
+        <v>45.22499999999999</v>
       </c>
       <c r="F77">
-        <v>71.02500000000001</v>
+        <v>45.22499999999999</v>
       </c>
       <c r="G77">
         <v>0</v>
       </c>
       <c r="H77">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -7484,37 +7484,37 @@
         <v>2.801</v>
       </c>
       <c r="M77">
-        <v>11.25434239590965</v>
+        <v>10.79973</v>
       </c>
       <c r="N77">
-        <v>-8.453342395909651</v>
+        <v>-7.998729999999998</v>
       </c>
       <c r="O77">
-        <v>-2.536002718772895</v>
+        <v>-2.399619</v>
       </c>
       <c r="P77">
-        <v>-5.917339677136756</v>
+        <v>-5.599110999999999</v>
       </c>
       <c r="Q77">
-        <v>-5.518339677136756</v>
+        <v>-5.200110999999999</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3786356362861396</v>
+        <v>0.6176183724655826</v>
       </c>
       <c r="T77">
-        <v>3.85011600946237</v>
+        <v>3.756608718034201</v>
       </c>
       <c r="U77">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V77">
-        <v>0.07466451352194545</v>
+        <v>0.07780750074307416</v>
       </c>
       <c r="W77">
-        <v>0.14662502493361</v>
+        <v>0.2202195688225539</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2488817117398181</v>
+        <v>0.2593583358102471</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7533,25 +7533,25 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.206061238475144</v>
+        <v>0.3215692697333111</v>
       </c>
       <c r="C78">
-        <v>-24.22797623008115</v>
+        <v>-13.0576935927055</v>
       </c>
       <c r="D78">
-        <v>47.74402376991885</v>
+        <v>32.77030640729449</v>
       </c>
       <c r="E78">
-        <v>71.97200000000001</v>
+        <v>45.828</v>
       </c>
       <c r="F78">
-        <v>71.97200000000001</v>
+        <v>45.828</v>
       </c>
       <c r="G78">
         <v>0</v>
       </c>
       <c r="H78">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -7566,37 +7566,37 @@
         <v>2.801</v>
       </c>
       <c r="M78">
-        <v>11.40440029452178</v>
+        <v>10.9437264</v>
       </c>
       <c r="N78">
-        <v>-8.60340029452178</v>
+        <v>-8.142726399999999</v>
       </c>
       <c r="O78">
-        <v>-2.581020088356534</v>
+        <v>-2.44281792</v>
       </c>
       <c r="P78">
-        <v>-6.022380206165247</v>
+        <v>-5.699908479999999</v>
       </c>
       <c r="Q78">
-        <v>-5.623380206165247</v>
+        <v>-5.300908479999999</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3937829544647288</v>
+        <v>0.6417358046516486</v>
       </c>
       <c r="T78">
-        <v>4.010537509856636</v>
+        <v>3.913134081285627</v>
       </c>
       <c r="U78">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V78">
-        <v>0.07368208571244615</v>
+        <v>0.07678371783856003</v>
       </c>
       <c r="W78">
-        <v>0.1467806965836961</v>
+        <v>0.2204640481801519</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2456069523748206</v>
+        <v>0.2559457261285334</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7615,25 +7615,25 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2074947991785455</v>
+        <v>0.3235692697333111</v>
       </c>
       <c r="C79">
-        <v>-25.53072366499651</v>
+        <v>-13.89084698276746</v>
       </c>
       <c r="D79">
-        <v>47.38827633500348</v>
+        <v>32.54015301723254</v>
       </c>
       <c r="E79">
-        <v>72.919</v>
+        <v>46.431</v>
       </c>
       <c r="F79">
-        <v>72.919</v>
+        <v>46.431</v>
       </c>
       <c r="G79">
         <v>0</v>
       </c>
       <c r="H79">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -7648,37 +7648,37 @@
         <v>2.801</v>
       </c>
       <c r="M79">
-        <v>11.55445819313391</v>
+        <v>11.0877228</v>
       </c>
       <c r="N79">
-        <v>-8.753458193133907</v>
+        <v>-8.2867228</v>
       </c>
       <c r="O79">
-        <v>-2.626037457940172</v>
+        <v>-2.48601684</v>
       </c>
       <c r="P79">
-        <v>-6.127420735193735</v>
+        <v>-5.800705959999999</v>
       </c>
       <c r="Q79">
-        <v>-5.728420735193735</v>
+        <v>-5.401705959999999</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.410247430745804</v>
+        <v>0.6679504048538942</v>
       </c>
       <c r="T79">
-        <v>4.184908705937359</v>
+        <v>4.083270345689351</v>
       </c>
       <c r="U79">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V79">
-        <v>0.07272517550838843</v>
+        <v>0.07578652669779949</v>
       </c>
       <c r="W79">
-        <v>0.1469323248142995</v>
+        <v>0.2207021774245655</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2424172516946281</v>
+        <v>0.2526217556593316</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7697,25 +7697,25 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.2089283598819471</v>
+        <v>0.3255692697333111</v>
       </c>
       <c r="C80">
-        <v>-26.8282088612659</v>
+        <v>-14.72079007919822</v>
       </c>
       <c r="D80">
-        <v>47.0377911387341</v>
+        <v>32.31320992080177</v>
       </c>
       <c r="E80">
-        <v>73.866</v>
+        <v>47.034</v>
       </c>
       <c r="F80">
-        <v>73.866</v>
+        <v>47.034</v>
       </c>
       <c r="G80">
         <v>0</v>
       </c>
       <c r="H80">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -7730,37 +7730,37 @@
         <v>2.801</v>
       </c>
       <c r="M80">
-        <v>11.70451609174604</v>
+        <v>11.2317192</v>
       </c>
       <c r="N80">
-        <v>-8.903516091746036</v>
+        <v>-8.4307192</v>
       </c>
       <c r="O80">
-        <v>-2.671054827523811</v>
+        <v>-2.52921576</v>
       </c>
       <c r="P80">
-        <v>-6.232461264222225</v>
+        <v>-5.90150344</v>
       </c>
       <c r="Q80">
-        <v>-5.833461264222225</v>
+        <v>-5.50250344</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.428208677597886</v>
+        <v>0.6965481505290712</v>
       </c>
       <c r="T80">
-        <v>4.375131828934512</v>
+        <v>4.268873543220684</v>
       </c>
       <c r="U80">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V80">
-        <v>0.07179280146340909</v>
+        <v>0.07481490456064822</v>
       </c>
       <c r="W80">
-        <v>0.1470800651415541</v>
+        <v>0.2209342007909172</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2393093382113636</v>
+        <v>0.2493830152021607</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7779,25 +7779,25 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2103619205853487</v>
+        <v>0.3275692697333111</v>
       </c>
       <c r="C81">
-        <v>-28.12054772072788</v>
+        <v>-15.54758958494649</v>
       </c>
       <c r="D81">
-        <v>46.69245227927212</v>
+        <v>32.08941041505351</v>
       </c>
       <c r="E81">
-        <v>74.813</v>
+        <v>47.637</v>
       </c>
       <c r="F81">
-        <v>74.813</v>
+        <v>47.637</v>
       </c>
       <c r="G81">
         <v>0</v>
       </c>
       <c r="H81">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -7812,37 +7812,37 @@
         <v>2.801</v>
       </c>
       <c r="M81">
-        <v>11.85457399035817</v>
+        <v>11.3757156</v>
       </c>
       <c r="N81">
-        <v>-9.053573990358165</v>
+        <v>-8.574715600000001</v>
       </c>
       <c r="O81">
-        <v>-2.71607219710745</v>
+        <v>-2.572414680000001</v>
       </c>
       <c r="P81">
-        <v>-6.337501793250716</v>
+        <v>-6.002300920000001</v>
       </c>
       <c r="Q81">
-        <v>-5.938501793250716</v>
+        <v>-5.603300920000001</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.4478805193882615</v>
+        <v>0.7278694910304555</v>
       </c>
       <c r="T81">
-        <v>4.583471439836155</v>
+        <v>4.472153235755003</v>
       </c>
       <c r="U81">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V81">
-        <v>0.07088403182463175</v>
+        <v>0.07386788045228558</v>
       </c>
       <c r="W81">
-        <v>0.1472240652073592</v>
+        <v>0.2211603501479942</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2362801060821058</v>
+        <v>0.2462262681742852</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7861,25 +7861,25 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2117954812887503</v>
+        <v>0.3295692697333111</v>
       </c>
       <c r="C82">
-        <v>-29.40785276634688</v>
+        <v>-16.37131036774782</v>
       </c>
       <c r="D82">
-        <v>46.35214723365313</v>
+        <v>31.86868963225218</v>
       </c>
       <c r="E82">
-        <v>75.76000000000001</v>
+        <v>48.24</v>
       </c>
       <c r="F82">
-        <v>75.76000000000001</v>
+        <v>48.24</v>
       </c>
       <c r="G82">
         <v>0</v>
       </c>
       <c r="H82">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -7894,37 +7894,37 @@
         <v>2.801</v>
       </c>
       <c r="M82">
-        <v>12.00463188897029</v>
+        <v>11.519712</v>
       </c>
       <c r="N82">
-        <v>-9.203631888970294</v>
+        <v>-8.718712000000002</v>
       </c>
       <c r="O82">
-        <v>-2.761089566691088</v>
+        <v>-2.615613600000001</v>
       </c>
       <c r="P82">
-        <v>-6.442542322279206</v>
+        <v>-6.1030984</v>
       </c>
       <c r="Q82">
-        <v>-6.043542322279206</v>
+        <v>-5.7040984</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.4695195453576746</v>
+        <v>0.7623229655819783</v>
       </c>
       <c r="T82">
-        <v>4.812645011827963</v>
+        <v>4.695760897542753</v>
       </c>
       <c r="U82">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V82">
-        <v>0.06999798142682385</v>
+        <v>0.072944531946632</v>
       </c>
       <c r="W82">
-        <v>0.1473644652715192</v>
+        <v>0.2213808457711443</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -7932,7 +7932,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2333266047560795</v>
+        <v>0.2431484398221067</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -7943,25 +7943,25 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2132290419921519</v>
+        <v>0.331569269733311</v>
       </c>
       <c r="C83">
-        <v>-30.69023326445216</v>
+        <v>-17.19201552280922</v>
       </c>
       <c r="D83">
-        <v>46.01676673554785</v>
+        <v>31.65098447719078</v>
       </c>
       <c r="E83">
-        <v>76.70700000000001</v>
+        <v>48.843</v>
       </c>
       <c r="F83">
-        <v>76.70700000000001</v>
+        <v>48.843</v>
       </c>
       <c r="G83">
         <v>0</v>
       </c>
       <c r="H83">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -7976,37 +7976,37 @@
         <v>2.801</v>
       </c>
       <c r="M83">
-        <v>12.15468978758242</v>
+        <v>11.6637084</v>
       </c>
       <c r="N83">
-        <v>-9.353689787582423</v>
+        <v>-8.862708400000001</v>
       </c>
       <c r="O83">
-        <v>-2.806106936274727</v>
+        <v>-2.658812520000001</v>
       </c>
       <c r="P83">
-        <v>-6.547582851307697</v>
+        <v>-6.20389588</v>
       </c>
       <c r="Q83">
-        <v>-6.148582851307697</v>
+        <v>-5.80489588</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.4934363635343944</v>
+        <v>0.8004031216652403</v>
       </c>
       <c r="T83">
-        <v>5.065942117713647</v>
+        <v>4.942906207939739</v>
       </c>
       <c r="U83">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V83">
-        <v>0.06913380881661614</v>
+        <v>0.07204398216951309</v>
       </c>
       <c r="W83">
-        <v>0.1475013986674283</v>
+        <v>0.2215958970579203</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2304460293887205</v>
+        <v>0.2401466072317103</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8025,25 +8025,25 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2146626026955534</v>
+        <v>0.3335692697333111</v>
       </c>
       <c r="C84">
-        <v>-31.96779534170827</v>
+        <v>-18.00976643294192</v>
       </c>
       <c r="D84">
-        <v>45.68620465829174</v>
+        <v>31.43623356705808</v>
       </c>
       <c r="E84">
-        <v>77.65400000000001</v>
+        <v>49.446</v>
       </c>
       <c r="F84">
-        <v>77.65400000000001</v>
+        <v>49.446</v>
       </c>
       <c r="G84">
         <v>0</v>
       </c>
       <c r="H84">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -8058,37 +8058,37 @@
         <v>2.801</v>
       </c>
       <c r="M84">
-        <v>12.30474768619455</v>
+        <v>11.8077048</v>
       </c>
       <c r="N84">
-        <v>-9.503747686194552</v>
+        <v>-9.0067048</v>
       </c>
       <c r="O84">
-        <v>-2.851124305858366</v>
+        <v>-2.70201144</v>
       </c>
       <c r="P84">
-        <v>-6.652623380336187</v>
+        <v>-6.30469336</v>
       </c>
       <c r="Q84">
-        <v>-6.253623380336187</v>
+        <v>-5.90569336</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.5200106059529719</v>
+        <v>0.8427144062021983</v>
       </c>
       <c r="T84">
-        <v>5.347383346475516</v>
+        <v>5.217512108380837</v>
       </c>
       <c r="U84">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V84">
-        <v>0.06829071358714522</v>
+        <v>0.07116539702110442</v>
       </c>
       <c r="W84">
-        <v>0.1476349922244128</v>
+        <v>0.2218057031913603</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2276357119571507</v>
+        <v>0.2372179900703479</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8107,25 +8107,25 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.216096163398955</v>
+        <v>0.3355692697333111</v>
       </c>
       <c r="C85">
-        <v>-33.24064209707986</v>
+        <v>-18.82462282626263</v>
       </c>
       <c r="D85">
-        <v>45.36035790292015</v>
+        <v>31.22437717373737</v>
       </c>
       <c r="E85">
-        <v>78.60100000000001</v>
+        <v>50.049</v>
       </c>
       <c r="F85">
-        <v>78.60100000000001</v>
+        <v>50.049</v>
       </c>
       <c r="G85">
         <v>0</v>
       </c>
       <c r="H85">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I85">
         <v>0</v>
@@ -8140,37 +8140,37 @@
         <v>2.801</v>
       </c>
       <c r="M85">
-        <v>12.45480558480668</v>
+        <v>11.9517012</v>
       </c>
       <c r="N85">
-        <v>-9.653805584806681</v>
+        <v>-9.1507012</v>
       </c>
       <c r="O85">
-        <v>-2.896141675442004</v>
+        <v>-2.745210360000001</v>
       </c>
       <c r="P85">
-        <v>-6.757663909364677</v>
+        <v>-6.40549084</v>
       </c>
       <c r="Q85">
-        <v>-6.358663909364677</v>
+        <v>-6.00649084</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.5497112298325585</v>
+        <v>0.8900034889199748</v>
       </c>
       <c r="T85">
-        <v>5.661935308032899</v>
+        <v>5.524424585344416</v>
       </c>
       <c r="U85">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V85">
-        <v>0.06746793390537238</v>
+        <v>0.07030798259916339</v>
       </c>
       <c r="W85">
-        <v>0.1477653666595422</v>
+        <v>0.2220104537553198</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8178,7 +8178,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2248931130179079</v>
+        <v>0.2343599419972112</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8189,25 +8189,25 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2175297241023565</v>
+        <v>0.337569269733311</v>
       </c>
       <c r="C86">
-        <v>-34.50887370903907</v>
+        <v>-19.63664283157714</v>
       </c>
       <c r="D86">
-        <v>45.03912629096094</v>
+        <v>31.01535716842285</v>
       </c>
       <c r="E86">
-        <v>79.548</v>
+        <v>50.65199999999999</v>
       </c>
       <c r="F86">
-        <v>79.548</v>
+        <v>50.65199999999999</v>
       </c>
       <c r="G86">
         <v>0</v>
       </c>
       <c r="H86">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I86">
         <v>0</v>
@@ -8222,37 +8222,37 @@
         <v>2.801</v>
       </c>
       <c r="M86">
-        <v>12.60486348341881</v>
+        <v>12.0956976</v>
       </c>
       <c r="N86">
-        <v>-9.803863483418809</v>
+        <v>-9.294697599999999</v>
       </c>
       <c r="O86">
-        <v>-2.941159045025643</v>
+        <v>-2.78840928</v>
       </c>
       <c r="P86">
-        <v>-6.862704438393166</v>
+        <v>-6.506288319999999</v>
       </c>
       <c r="Q86">
-        <v>-6.463704438393166</v>
+        <v>-6.107288319999999</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.583124431697093</v>
+        <v>0.9432037069774726</v>
       </c>
       <c r="T86">
-        <v>6.015806264784952</v>
+        <v>5.869701121928439</v>
       </c>
       <c r="U86">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V86">
-        <v>0.06666474421602271</v>
+        <v>0.06947098280631621</v>
       </c>
       <c r="W86">
-        <v>0.1478926369414543</v>
+        <v>0.2222103293058517</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2222158140534091</v>
+        <v>0.2315699426877207</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8271,25 +8271,25 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.2189632848057581</v>
+        <v>0.3395692697333111</v>
       </c>
       <c r="C87">
-        <v>-35.77258753824957</v>
+        <v>-20.44588303155452</v>
       </c>
       <c r="D87">
-        <v>44.72241246175044</v>
+        <v>30.80911696844547</v>
       </c>
       <c r="E87">
-        <v>80.495</v>
+        <v>51.255</v>
       </c>
       <c r="F87">
-        <v>80.495</v>
+        <v>51.255</v>
       </c>
       <c r="G87">
         <v>0</v>
       </c>
       <c r="H87">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I87">
         <v>0</v>
@@ -8304,37 +8304,37 @@
         <v>2.801</v>
       </c>
       <c r="M87">
-        <v>12.75492138203094</v>
+        <v>12.239694</v>
       </c>
       <c r="N87">
-        <v>-9.953921382030938</v>
+        <v>-9.438694</v>
       </c>
       <c r="O87">
-        <v>-2.986176414609281</v>
+        <v>-2.8316082</v>
       </c>
       <c r="P87">
-        <v>-6.967744967421657</v>
+        <v>-6.6070858</v>
       </c>
       <c r="Q87">
-        <v>-6.568744967421657</v>
+        <v>-6.2080858</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.620992727143566</v>
+        <v>1.003497287442638</v>
       </c>
       <c r="T87">
-        <v>6.416860015770617</v>
+        <v>6.261014530057002</v>
       </c>
       <c r="U87">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V87">
-        <v>0.06588045310759892</v>
+        <v>0.0686536771262419</v>
       </c>
       <c r="W87">
-        <v>0.1480169126284979</v>
+        <v>0.2224055019022534</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8342,7 +8342,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.219601510358663</v>
+        <v>0.2288455904208063</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8353,25 +8353,25 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.2203968455091597</v>
+        <v>0.341569269733311</v>
       </c>
       <c r="C88">
-        <v>-37.03187822594852</v>
+        <v>-21.25239851379341</v>
       </c>
       <c r="D88">
-        <v>44.41012177405148</v>
+        <v>30.60560148620659</v>
       </c>
       <c r="E88">
-        <v>81.44200000000001</v>
+        <v>51.858</v>
       </c>
       <c r="F88">
-        <v>81.44200000000001</v>
+        <v>51.858</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I88">
         <v>0</v>
@@ -8386,37 +8386,37 @@
         <v>2.801</v>
       </c>
       <c r="M88">
-        <v>12.90497928064307</v>
+        <v>12.3836904</v>
       </c>
       <c r="N88">
-        <v>-10.10397928064307</v>
+        <v>-9.582690400000001</v>
       </c>
       <c r="O88">
-        <v>-3.03119378419292</v>
+        <v>-2.874807120000001</v>
       </c>
       <c r="P88">
-        <v>-7.072785496450146</v>
+        <v>-6.70788328</v>
       </c>
       <c r="Q88">
-        <v>-6.673785496450146</v>
+        <v>-6.30888328</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.6642707790823922</v>
+        <v>1.072404236545683</v>
       </c>
       <c r="T88">
-        <v>6.875207159754232</v>
+        <v>6.708229853632502</v>
       </c>
       <c r="U88">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V88">
-        <v>0.065114401327278</v>
+        <v>0.06785537855500652</v>
       </c>
       <c r="W88">
-        <v>0.1481382981832846</v>
+        <v>0.2225961356010644</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8424,7 +8424,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.21704800442426</v>
+        <v>0.226184595183355</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.2218304062125613</v>
+        <v>0.343569269733311</v>
       </c>
       <c r="C89">
-        <v>-38.28683778823515</v>
+        <v>-22.05624291987797</v>
       </c>
       <c r="D89">
-        <v>44.10216221176485</v>
+        <v>30.40475708012203</v>
       </c>
       <c r="E89">
-        <v>82.389</v>
+        <v>52.461</v>
       </c>
       <c r="F89">
-        <v>82.389</v>
+        <v>52.461</v>
       </c>
       <c r="G89">
         <v>0</v>
       </c>
       <c r="H89">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I89">
         <v>0</v>
@@ -8468,37 +8468,37 @@
         <v>2.801</v>
       </c>
       <c r="M89">
-        <v>13.05503717925519</v>
+        <v>12.5276868</v>
       </c>
       <c r="N89">
-        <v>-10.25403717925519</v>
+        <v>-9.7266868</v>
       </c>
       <c r="O89">
-        <v>-3.076211153776558</v>
+        <v>-2.91800604</v>
       </c>
       <c r="P89">
-        <v>-7.177826025478636</v>
+        <v>-6.80868076</v>
       </c>
       <c r="Q89">
-        <v>-6.778826025478636</v>
+        <v>-6.40968076</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.7142069928579609</v>
+        <v>1.151912254741505</v>
       </c>
       <c r="T89">
-        <v>7.404069248966096</v>
+        <v>7.224247534681156</v>
       </c>
       <c r="U89">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V89">
-        <v>0.0643659599327116</v>
+        <v>0.06707543167506393</v>
       </c>
       <c r="W89">
-        <v>0.1482568932655475</v>
+        <v>0.2227823869159948</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2145531997757053</v>
+        <v>0.223584772250213</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8517,25 +8517,25 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.2232639669159628</v>
+        <v>0.3455692697333111</v>
       </c>
       <c r="C90">
-        <v>-39.53755570646329</v>
+        <v>-22.85746849251473</v>
       </c>
       <c r="D90">
-        <v>43.7984442935367</v>
+        <v>30.20653150748527</v>
       </c>
       <c r="E90">
-        <v>83.336</v>
+        <v>53.064</v>
       </c>
       <c r="F90">
-        <v>83.336</v>
+        <v>53.064</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
       <c r="H90">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I90">
         <v>0</v>
@@ -8550,37 +8550,37 @@
         <v>2.801</v>
       </c>
       <c r="M90">
-        <v>13.20509507786732</v>
+        <v>12.6716832</v>
       </c>
       <c r="N90">
-        <v>-10.40409507786732</v>
+        <v>-9.8706832</v>
       </c>
       <c r="O90">
-        <v>-3.121228523360197</v>
+        <v>-2.96120496</v>
       </c>
       <c r="P90">
-        <v>-7.282866554507127</v>
+        <v>-6.90947824</v>
       </c>
       <c r="Q90">
-        <v>-6.883866554507127</v>
+        <v>-6.51047824</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.7724659089294577</v>
+        <v>1.244671609303297</v>
       </c>
       <c r="T90">
-        <v>8.021075019713273</v>
+        <v>7.826268162571254</v>
       </c>
       <c r="U90">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V90">
-        <v>0.06363452856983987</v>
+        <v>0.06631321086057455</v>
       </c>
       <c r="W90">
-        <v>0.1483727930050317</v>
+        <v>0.2229644052464948</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8588,7 +8588,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2121150952327996</v>
+        <v>0.2210440362019152</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8599,25 +8599,25 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.2246975276193644</v>
+        <v>0.347569269733311</v>
       </c>
       <c r="C91">
-        <v>-40.78411901392445</v>
+        <v>-23.65612612083749</v>
       </c>
       <c r="D91">
-        <v>43.49888098607556</v>
+        <v>30.01087387916251</v>
       </c>
       <c r="E91">
-        <v>84.283</v>
+        <v>53.667</v>
       </c>
       <c r="F91">
-        <v>84.283</v>
+        <v>53.667</v>
       </c>
       <c r="G91">
         <v>0</v>
       </c>
       <c r="H91">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I91">
         <v>0</v>
@@ -8632,37 +8632,37 @@
         <v>2.801</v>
       </c>
       <c r="M91">
-        <v>13.35515297647945</v>
+        <v>12.8156796</v>
       </c>
       <c r="N91">
-        <v>-10.55415297647945</v>
+        <v>-10.0146796</v>
       </c>
       <c r="O91">
-        <v>-3.166245892943836</v>
+        <v>-3.004403880000001</v>
       </c>
       <c r="P91">
-        <v>-7.387907083535616</v>
+        <v>-7.01027572</v>
       </c>
       <c r="Q91">
-        <v>-6.988907083535616</v>
+        <v>-6.61127572</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.841317355195772</v>
+        <v>1.354296301058142</v>
       </c>
       <c r="T91">
-        <v>8.750263657869024</v>
+        <v>8.537747086441367</v>
       </c>
       <c r="U91">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V91">
-        <v>0.06291953386680796</v>
+        <v>0.06556811860371416</v>
       </c>
       <c r="W91">
-        <v>0.1484860882559882</v>
+        <v>0.2231423332774331</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2097317795560265</v>
+        <v>0.2185603953457138</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8681,25 +8681,25 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.226131088322766</v>
+        <v>0.349569269733311</v>
       </c>
       <c r="C92">
-        <v>-42.02661237899777</v>
+        <v>-24.45226538396293</v>
       </c>
       <c r="D92">
-        <v>43.20338762100224</v>
+        <v>29.81773461603707</v>
       </c>
       <c r="E92">
-        <v>85.23</v>
+        <v>54.27</v>
       </c>
       <c r="F92">
-        <v>85.23</v>
+        <v>54.27</v>
       </c>
       <c r="G92">
         <v>0</v>
       </c>
       <c r="H92">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -8714,37 +8714,37 @@
         <v>2.801</v>
       </c>
       <c r="M92">
-        <v>13.50521087509158</v>
+        <v>12.959676</v>
       </c>
       <c r="N92">
-        <v>-10.70421087509158</v>
+        <v>-10.158676</v>
       </c>
       <c r="O92">
-        <v>-3.211263262527474</v>
+        <v>-3.0476028</v>
       </c>
       <c r="P92">
-        <v>-7.492947612564107</v>
+        <v>-7.1110732</v>
       </c>
       <c r="Q92">
-        <v>-7.093947612564107</v>
+        <v>-6.7120732</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.9239390907153492</v>
+        <v>1.485845931163957</v>
       </c>
       <c r="T92">
-        <v>9.625290023655927</v>
+        <v>9.391521795085506</v>
       </c>
       <c r="U92">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V92">
-        <v>0.06222042793495454</v>
+        <v>0.06483958395256179</v>
       </c>
       <c r="W92">
-        <v>0.1485968658347012</v>
+        <v>0.2233163073521283</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8752,7 +8752,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2074014264498485</v>
+        <v>0.2161319465085393</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8763,25 +8763,25 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2275646490261675</v>
+        <v>0.351569269733311</v>
       </c>
       <c r="C93">
-        <v>-43.26511818493383</v>
+        <v>-25.24593459287506</v>
       </c>
       <c r="D93">
-        <v>42.91188181506618</v>
+        <v>29.62706540712494</v>
       </c>
       <c r="E93">
-        <v>86.17700000000001</v>
+        <v>54.873</v>
       </c>
       <c r="F93">
-        <v>86.17700000000001</v>
+        <v>54.873</v>
       </c>
       <c r="G93">
         <v>0</v>
       </c>
       <c r="H93">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -8796,37 +8796,37 @@
         <v>2.801</v>
       </c>
       <c r="M93">
-        <v>13.65526877370371</v>
+        <v>13.1036724</v>
       </c>
       <c r="N93">
-        <v>-10.85426877370371</v>
+        <v>-10.3026724</v>
       </c>
       <c r="O93">
-        <v>-3.256280632111113</v>
+        <v>-3.09080172</v>
       </c>
       <c r="P93">
-        <v>-7.597988141592597</v>
+        <v>-7.211870680000001</v>
       </c>
       <c r="Q93">
-        <v>-7.198988141592597</v>
+        <v>-6.812870680000001</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>1.024921211905944</v>
+        <v>1.646628812404396</v>
       </c>
       <c r="T93">
-        <v>10.69476669295103</v>
+        <v>10.43502421676167</v>
       </c>
       <c r="U93">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V93">
-        <v>0.06153668696863634</v>
+        <v>0.06412706105198418</v>
       </c>
       <c r="W93">
-        <v>0.1487052087413545</v>
+        <v>0.2234864578207862</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2051222898954546</v>
+        <v>0.2137568701732806</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8845,25 +8845,25 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2289982097295691</v>
+        <v>0.3535692697333111</v>
       </c>
       <c r="C94">
-        <v>-44.49971660643006</v>
+        <v>-26.03718083071287</v>
       </c>
       <c r="D94">
-        <v>42.62428339356995</v>
+        <v>29.43881916928713</v>
       </c>
       <c r="E94">
-        <v>87.12400000000001</v>
+        <v>55.476</v>
       </c>
       <c r="F94">
-        <v>87.12400000000001</v>
+        <v>55.476</v>
       </c>
       <c r="G94">
         <v>0</v>
       </c>
       <c r="H94">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I94">
         <v>0</v>
@@ -8878,37 +8878,37 @@
         <v>2.801</v>
       </c>
       <c r="M94">
-        <v>13.80532667231584</v>
+        <v>13.2476688</v>
       </c>
       <c r="N94">
-        <v>-11.00432667231584</v>
+        <v>-10.4466688</v>
       </c>
       <c r="O94">
-        <v>-3.301298001694752</v>
+        <v>-3.13400064</v>
       </c>
       <c r="P94">
-        <v>-7.703028670621087</v>
+        <v>-7.312668159999999</v>
       </c>
       <c r="Q94">
-        <v>-7.304028670621087</v>
+        <v>-6.913668159999999</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>1.151148863394187</v>
+        <v>1.847607413954947</v>
       </c>
       <c r="T94">
-        <v>12.03161252956991</v>
+        <v>11.73940224385689</v>
       </c>
       <c r="U94">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V94">
-        <v>0.06086780993636857</v>
+        <v>0.06343002777968001</v>
       </c>
       <c r="W94">
-        <v>0.1488111963674285</v>
+        <v>0.2236529093662124</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -8916,7 +8916,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2028926997878953</v>
+        <v>0.2114334259322667</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -8927,25 +8927,25 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2304317704329707</v>
+        <v>0.3555692697333111</v>
       </c>
       <c r="C95">
-        <v>-45.7304856831474</v>
+        <v>-26.82604999153186</v>
       </c>
       <c r="D95">
-        <v>42.34051431685261</v>
+        <v>29.25295000846814</v>
       </c>
       <c r="E95">
-        <v>88.07100000000001</v>
+        <v>56.079</v>
       </c>
       <c r="F95">
-        <v>88.07100000000001</v>
+        <v>56.079</v>
       </c>
       <c r="G95">
         <v>0</v>
       </c>
       <c r="H95">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I95">
         <v>0</v>
@@ -8960,37 +8960,37 @@
         <v>2.801</v>
       </c>
       <c r="M95">
-        <v>13.95538457092797</v>
+        <v>13.3916652</v>
       </c>
       <c r="N95">
-        <v>-11.15438457092797</v>
+        <v>-10.5906652</v>
       </c>
       <c r="O95">
-        <v>-3.34631537127839</v>
+        <v>-3.17719956</v>
       </c>
       <c r="P95">
-        <v>-7.808069199649578</v>
+        <v>-7.41346564</v>
       </c>
       <c r="Q95">
-        <v>-7.409069199649578</v>
+        <v>-7.01446564</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.313441558164785</v>
+        <v>2.106008473091368</v>
       </c>
       <c r="T95">
-        <v>13.75041431950847</v>
+        <v>13.41645970726501</v>
       </c>
       <c r="U95">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V95">
-        <v>0.06021331735640761</v>
+        <v>0.06274798447022108</v>
       </c>
       <c r="W95">
-        <v>0.1489149046897159</v>
+        <v>0.2238157813085112</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.200711057854692</v>
+        <v>0.2091599482340702</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9009,25 +9009,25 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2318653311363722</v>
+        <v>0.3575692697333111</v>
       </c>
       <c r="C96">
-        <v>-46.95750139030983</v>
+        <v>-27.61258681760636</v>
       </c>
       <c r="D96">
-        <v>42.06049860969019</v>
+        <v>29.06941318239364</v>
       </c>
       <c r="E96">
-        <v>89.01800000000001</v>
+        <v>56.682</v>
       </c>
       <c r="F96">
-        <v>89.01800000000001</v>
+        <v>56.682</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -9042,37 +9042,37 @@
         <v>2.801</v>
       </c>
       <c r="M96">
-        <v>14.1054424695401</v>
+        <v>13.5356616</v>
       </c>
       <c r="N96">
-        <v>-11.3044424695401</v>
+        <v>-10.7346616</v>
       </c>
       <c r="O96">
-        <v>-3.391332740862029</v>
+        <v>-3.220398480000001</v>
       </c>
       <c r="P96">
-        <v>-7.913109728678068</v>
+        <v>-7.514263120000001</v>
       </c>
       <c r="Q96">
-        <v>-7.514109728678068</v>
+        <v>-7.115263120000001</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.529831817858916</v>
+        <v>2.450543218606597</v>
       </c>
       <c r="T96">
-        <v>16.04215003942656</v>
+        <v>15.65253632514252</v>
       </c>
       <c r="U96">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V96">
-        <v>0.05957275015048838</v>
+        <v>0.06208045272053788</v>
       </c>
       <c r="W96">
-        <v>0.1490164064519546</v>
+        <v>0.2239751878903356</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1985758338349612</v>
+        <v>0.2069348424017929</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9091,25 +9091,25 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2332988918397738</v>
+        <v>0.3595692697333112</v>
       </c>
       <c r="C97">
-        <v>-48.18083770652083</v>
+        <v>-28.39683493533636</v>
       </c>
       <c r="D97">
-        <v>41.78416229347918</v>
+        <v>28.88816506466364</v>
       </c>
       <c r="E97">
-        <v>89.965</v>
+        <v>57.285</v>
       </c>
       <c r="F97">
-        <v>89.965</v>
+        <v>57.285</v>
       </c>
       <c r="G97">
         <v>0</v>
       </c>
       <c r="H97">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -9124,37 +9124,37 @@
         <v>2.801</v>
       </c>
       <c r="M97">
-        <v>14.25550036815222</v>
+        <v>13.679658</v>
       </c>
       <c r="N97">
-        <v>-11.45450036815222</v>
+        <v>-10.878658</v>
       </c>
       <c r="O97">
-        <v>-3.436350110445667</v>
+        <v>-3.263597400000001</v>
       </c>
       <c r="P97">
-        <v>-8.018150257706557</v>
+        <v>-7.615060600000001</v>
       </c>
       <c r="Q97">
-        <v>-7.619150257706557</v>
+        <v>-7.2160606</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.8327781814307</v>
+        <v>2.932891862327918</v>
       </c>
       <c r="T97">
-        <v>19.25058004731187</v>
+        <v>18.78304359017104</v>
       </c>
       <c r="U97">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V97">
-        <v>0.05894566856995693</v>
+        <v>0.061426974270848</v>
       </c>
       <c r="W97">
-        <v>0.1491157713349883</v>
+        <v>0.2241312385441215</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9162,7 +9162,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1964855618998564</v>
+        <v>0.2047565809028267</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9173,25 +9173,25 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2347324525431754</v>
+        <v>0.361569269733311</v>
       </c>
       <c r="C98">
-        <v>-49.40056667892399</v>
+        <v>-29.17883688981939</v>
       </c>
       <c r="D98">
-        <v>41.51143332107602</v>
+        <v>28.70916311018061</v>
       </c>
       <c r="E98">
-        <v>90.91200000000001</v>
+        <v>57.888</v>
       </c>
       <c r="F98">
-        <v>90.91200000000001</v>
+        <v>57.888</v>
       </c>
       <c r="G98">
         <v>0</v>
       </c>
       <c r="H98">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -9206,37 +9206,37 @@
         <v>2.801</v>
       </c>
       <c r="M98">
-        <v>14.40555826676435</v>
+        <v>13.8236544</v>
       </c>
       <c r="N98">
-        <v>-11.60455826676435</v>
+        <v>-11.0226544</v>
       </c>
       <c r="O98">
-        <v>-3.481367480029306</v>
+        <v>-3.306796320000001</v>
       </c>
       <c r="P98">
-        <v>-8.123190786735048</v>
+        <v>-7.71585808</v>
       </c>
       <c r="Q98">
-        <v>-7.724190786735048</v>
+        <v>-7.31685808</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>2.287197726788371</v>
+        <v>3.656414827909888</v>
       </c>
       <c r="T98">
-        <v>24.06322505913979</v>
+        <v>23.47880448771374</v>
       </c>
       <c r="U98">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V98">
-        <v>0.05833165118901987</v>
+        <v>0.06078710995552667</v>
       </c>
       <c r="W98">
-        <v>0.1492130661162921</v>
+        <v>0.2242840381426202</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1944388372967329</v>
+        <v>0.2026236998517555</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9255,25 +9255,25 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.236166013246577</v>
+        <v>0.3635692697333111</v>
       </c>
       <c r="C99">
-        <v>-50.61675848582825</v>
+        <v>-29.95863417814506</v>
       </c>
       <c r="D99">
-        <v>41.24224151417175</v>
+        <v>28.53236582185493</v>
       </c>
       <c r="E99">
-        <v>91.85899999999999</v>
+        <v>58.49099999999999</v>
       </c>
       <c r="F99">
-        <v>91.85899999999999</v>
+        <v>58.49099999999999</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
       <c r="H99">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -9288,37 +9288,37 @@
         <v>2.801</v>
       </c>
       <c r="M99">
-        <v>14.55561616537648</v>
+        <v>13.9676508</v>
       </c>
       <c r="N99">
-        <v>-11.75461616537648</v>
+        <v>-11.1666508</v>
       </c>
       <c r="O99">
-        <v>-3.526384849612944</v>
+        <v>-3.34999524</v>
       </c>
       <c r="P99">
-        <v>-8.228231315763535</v>
+        <v>-7.816655559999999</v>
       </c>
       <c r="Q99">
-        <v>-7.829231315763535</v>
+        <v>-7.417655559999999</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>3.044563635717828</v>
+        <v>4.862286437213185</v>
       </c>
       <c r="T99">
-        <v>32.08430007885306</v>
+        <v>31.30507265028499</v>
       </c>
       <c r="U99">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V99">
-        <v>0.0577302939602671</v>
+        <v>0.06016043871887176</v>
       </c>
       <c r="W99">
-        <v>0.149308354819631</v>
+        <v>0.2244336872339334</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9326,7 +9326,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1924343132008903</v>
+        <v>0.2005347957295726</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9337,25 +9337,25 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2375995739499785</v>
+        <v>0.3655692697333111</v>
       </c>
       <c r="C100">
-        <v>-51.82948149691233</v>
+        <v>-30.73626728146681</v>
       </c>
       <c r="D100">
-        <v>40.97651850308767</v>
+        <v>28.35773271853318</v>
       </c>
       <c r="E100">
-        <v>92.806</v>
+        <v>59.09399999999999</v>
       </c>
       <c r="F100">
-        <v>92.806</v>
+        <v>59.09399999999999</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I100">
         <v>0</v>
@@ -9370,37 +9370,37 @@
         <v>2.801</v>
       </c>
       <c r="M100">
-        <v>14.70567406398861</v>
+        <v>14.1116472</v>
       </c>
       <c r="N100">
-        <v>-11.90467406398861</v>
+        <v>-11.3106472</v>
       </c>
       <c r="O100">
-        <v>-3.571402219196583</v>
+        <v>-3.393194160000001</v>
       </c>
       <c r="P100">
-        <v>-8.333271844792026</v>
+        <v>-7.91745304</v>
       </c>
       <c r="Q100">
-        <v>-7.934271844792026</v>
+        <v>-7.51845304</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>4.559295453576742</v>
+        <v>7.274029655819776</v>
       </c>
       <c r="T100">
-        <v>48.12645011827959</v>
+        <v>46.95760897542748</v>
       </c>
       <c r="U100">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V100">
-        <v>0.05714120932801947</v>
+        <v>0.05954655669112817</v>
       </c>
       <c r="W100">
-        <v>0.1494016988555547</v>
+        <v>0.2245802822621586</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9408,7 +9408,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1904706977600649</v>
+        <v>0.1984885223037606</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9419,25 +9419,25 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2390331346533801</v>
+        <v>0.3675692697333111</v>
       </c>
       <c r="C101">
-        <v>-53.03880233111654</v>
+        <v>-31.51177569590309</v>
       </c>
       <c r="D101">
-        <v>40.71419766888346</v>
+        <v>28.18522430409691</v>
       </c>
       <c r="E101">
-        <v>93.753</v>
+        <v>59.697</v>
       </c>
       <c r="F101">
-        <v>93.753</v>
+        <v>59.697</v>
       </c>
       <c r="G101">
         <v>0</v>
       </c>
       <c r="H101">
-        <v>94.7</v>
+        <v>60.3</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -9452,37 +9452,37 @@
         <v>2.801</v>
       </c>
       <c r="M101">
-        <v>14.85573196260074</v>
+        <v>14.2556436</v>
       </c>
       <c r="N101">
-        <v>-12.05473196260074</v>
+        <v>-11.4546436</v>
       </c>
       <c r="O101">
-        <v>-3.616419588780222</v>
+        <v>-3.43639308</v>
       </c>
       <c r="P101">
-        <v>-8.438312373820517</v>
+        <v>-8.018250519999999</v>
       </c>
       <c r="Q101">
-        <v>-8.039312373820518</v>
+        <v>-7.619250519999999</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>9.103490907153484</v>
+        <v>14.50925931163955</v>
       </c>
       <c r="T101">
-        <v>96.25290023655917</v>
+        <v>93.91521795085495</v>
       </c>
       <c r="U101">
-        <v>0.158456070340157</v>
+        <v>0.2388</v>
       </c>
       <c r="V101">
-        <v>0.05656402539541321</v>
+        <v>0.05894507632051072</v>
       </c>
       <c r="W101">
-        <v>0.149493157153379</v>
+        <v>0.2247239157746621</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>0.1885467513180441</v>
+        <v>0.1964835877350357</v>
       </c>
       <c r="Z101">
         <v>0</v>
